--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -4187,32 +4187,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129096204</v>
+        <v>129100213</v>
       </c>
       <c r="B36" t="n">
-        <v>96770</v>
+        <v>79034</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4222,13 +4222,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>570894</v>
+        <v>570948</v>
       </c>
       <c r="R36" t="n">
-        <v>7057432</v>
+        <v>7057486</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4272,44 +4272,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129100213</v>
+        <v>129096204</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>96770</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4319,13 +4319,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570948</v>
+        <v>570894</v>
       </c>
       <c r="R37" t="n">
-        <v>7057486</v>
+        <v>7057432</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4369,12 +4369,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129100217</v>
       </c>
       <c r="B3" t="n">
-        <v>96770</v>
+        <v>96775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129094000</v>
+        <v>129094090</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +890,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570947</v>
+        <v>571144</v>
       </c>
       <c r="R4" t="n">
-        <v>7057312</v>
+        <v>7057314</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,19 +979,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129094153</v>
+        <v>129094000</v>
       </c>
       <c r="B5" t="n">
         <v>79034</v>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571029</v>
+        <v>570947</v>
       </c>
       <c r="R5" t="n">
-        <v>7057276</v>
+        <v>7057312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129094090</v>
+        <v>129094153</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,39 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571144</v>
+        <v>571029</v>
       </c>
       <c r="R6" t="n">
-        <v>7057314</v>
+        <v>7057276</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,12 +1193,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1208,7 +1208,7 @@
         <v>129096194</v>
       </c>
       <c r="B7" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>129096203</v>
       </c>
       <c r="B10" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>129100218</v>
       </c>
       <c r="B13" t="n">
-        <v>96770</v>
+        <v>96775</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>129100211</v>
       </c>
       <c r="B14" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129092344</v>
+        <v>129093213</v>
       </c>
       <c r="B16" t="n">
-        <v>91538</v>
+        <v>80139</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,21 +2143,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571249</v>
+        <v>570967</v>
       </c>
       <c r="R16" t="n">
-        <v>7057525</v>
+        <v>7057481</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2227,22 +2227,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129093213</v>
+        <v>129092344</v>
       </c>
       <c r="B17" t="n">
-        <v>80139</v>
+        <v>91541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,21 +2250,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570967</v>
+        <v>571249</v>
       </c>
       <c r="R17" t="n">
-        <v>7057481</v>
+        <v>7057525</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2334,22 +2334,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129096197</v>
+        <v>129092795</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,37 +2357,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570925</v>
+        <v>571218</v>
       </c>
       <c r="R18" t="n">
-        <v>7057499</v>
+        <v>7057576</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2414,9 +2419,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2431,22 +2446,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129092795</v>
+        <v>129096197</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,42 +2469,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571218</v>
+        <v>570925</v>
       </c>
       <c r="R19" t="n">
-        <v>7057576</v>
+        <v>7057499</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2516,19 +2526,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2543,12 +2543,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2655,7 +2655,7 @@
         <v>129096205</v>
       </c>
       <c r="B21" t="n">
-        <v>96770</v>
+        <v>96775</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2963,10 +2963,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129100212</v>
+        <v>129100202</v>
       </c>
       <c r="B24" t="n">
-        <v>91516</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,21 +2974,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>570991</v>
+        <v>571055</v>
       </c>
       <c r="R24" t="n">
-        <v>7057492</v>
+        <v>7057572</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3034,6 +3034,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3060,10 +3065,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129100202</v>
+        <v>129100212</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>91519</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,21 +3076,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3095,10 +3100,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571055</v>
+        <v>570991</v>
       </c>
       <c r="R25" t="n">
-        <v>7057572</v>
+        <v>7057492</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3131,11 +3136,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3262,7 +3262,7 @@
         <v>129093842</v>
       </c>
       <c r="B27" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>129092361</v>
       </c>
       <c r="B29" t="n">
-        <v>96770</v>
+        <v>96775</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>129093045</v>
       </c>
       <c r="B31" t="n">
-        <v>100812</v>
+        <v>100817</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129096206</v>
+        <v>129100194</v>
       </c>
       <c r="B32" t="n">
-        <v>96770</v>
+        <v>5197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2869</v>
+        <v>105930</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3829,13 +3829,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571159</v>
+        <v>571156</v>
       </c>
       <c r="R32" t="n">
-        <v>7057565</v>
+        <v>7057504</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3879,22 +3879,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129100194</v>
+        <v>129096206</v>
       </c>
       <c r="B33" t="n">
-        <v>5197</v>
+        <v>96775</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105930</v>
+        <v>2869</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3926,13 +3926,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571156</v>
+        <v>571159</v>
       </c>
       <c r="R33" t="n">
-        <v>7057504</v>
+        <v>7057565</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3976,12 +3976,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4093,7 +4093,7 @@
         <v>129100195</v>
       </c>
       <c r="B35" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,32 +4187,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129100213</v>
+        <v>129096204</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>96775</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4222,13 +4222,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>570948</v>
+        <v>570894</v>
       </c>
       <c r="R36" t="n">
-        <v>7057486</v>
+        <v>7057432</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4272,44 +4272,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129096204</v>
+        <v>129100213</v>
       </c>
       <c r="B37" t="n">
-        <v>96770</v>
+        <v>79034</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4319,13 +4319,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570894</v>
+        <v>570948</v>
       </c>
       <c r="R37" t="n">
-        <v>7057432</v>
+        <v>7057486</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4369,12 +4369,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4486,7 +4486,7 @@
         <v>129092519</v>
       </c>
       <c r="B39" t="n">
-        <v>100812</v>
+        <v>100817</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129093948</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129100217</v>
       </c>
       <c r="B3" t="n">
-        <v>96775</v>
+        <v>96778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129094090</v>
+        <v>129094000</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571144</v>
+        <v>570947</v>
       </c>
       <c r="R4" t="n">
-        <v>7057314</v>
+        <v>7057312</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +949,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +959,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129094000</v>
+        <v>129094153</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570947</v>
+        <v>571029</v>
       </c>
       <c r="R5" t="n">
-        <v>7057312</v>
+        <v>7057276</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129094153</v>
+        <v>129094090</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,34 +1104,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571029</v>
+        <v>571144</v>
       </c>
       <c r="R6" t="n">
-        <v>7057276</v>
+        <v>7057314</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,12 +1193,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1208,7 +1208,7 @@
         <v>129096194</v>
       </c>
       <c r="B7" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>129093962</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>129096203</v>
       </c>
       <c r="B10" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129091918</v>
+        <v>129100200</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1623,34 +1623,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571079</v>
+        <v>571163</v>
       </c>
       <c r="R11" t="n">
-        <v>7057562</v>
+        <v>7057489</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,19 +1680,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1707,22 +1697,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129100200</v>
+        <v>129091918</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,34 +1720,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571163</v>
+        <v>571079</v>
       </c>
       <c r="R12" t="n">
-        <v>7057489</v>
+        <v>7057562</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,9 +1777,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1804,12 +1804,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1819,7 +1819,7 @@
         <v>129100218</v>
       </c>
       <c r="B13" t="n">
-        <v>96775</v>
+        <v>96778</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>129100211</v>
       </c>
       <c r="B14" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129093213</v>
+        <v>129092344</v>
       </c>
       <c r="B16" t="n">
-        <v>80139</v>
+        <v>91544</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,21 +2143,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570967</v>
+        <v>571249</v>
       </c>
       <c r="R16" t="n">
-        <v>7057481</v>
+        <v>7057525</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2227,22 +2227,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129092344</v>
+        <v>129093213</v>
       </c>
       <c r="B17" t="n">
-        <v>91541</v>
+        <v>80140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,21 +2250,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571249</v>
+        <v>570967</v>
       </c>
       <c r="R17" t="n">
-        <v>7057525</v>
+        <v>7057481</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2334,22 +2334,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129092795</v>
+        <v>129096197</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,42 +2357,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571218</v>
+        <v>570925</v>
       </c>
       <c r="R18" t="n">
-        <v>7057576</v>
+        <v>7057499</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2419,19 +2414,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2446,22 +2431,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129096197</v>
+        <v>129092795</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,37 +2454,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570925</v>
+        <v>571218</v>
       </c>
       <c r="R19" t="n">
-        <v>7057499</v>
+        <v>7057576</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2526,9 +2516,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2543,12 +2543,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2558,7 +2558,7 @@
         <v>129100214</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>129096205</v>
       </c>
       <c r="B21" t="n">
-        <v>96775</v>
+        <v>96778</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>129100212</v>
       </c>
       <c r="B25" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>129096198</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>129093842</v>
       </c>
       <c r="B27" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3483,10 +3483,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129092361</v>
+        <v>129100204</v>
       </c>
       <c r="B29" t="n">
-        <v>96775</v>
+        <v>80168</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3494,34 +3494,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2869</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571258</v>
+        <v>570947</v>
       </c>
       <c r="R29" t="n">
-        <v>7057527</v>
+        <v>7057532</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,19 +3551,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3578,22 +3568,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129100204</v>
+        <v>129092361</v>
       </c>
       <c r="B30" t="n">
-        <v>80167</v>
+        <v>96778</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3601,34 +3591,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>2869</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>570947</v>
+        <v>571258</v>
       </c>
       <c r="R30" t="n">
-        <v>7057532</v>
+        <v>7057527</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,9 +3648,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3675,22 +3675,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129093045</v>
+        <v>129100194</v>
       </c>
       <c r="B31" t="n">
-        <v>100817</v>
+        <v>5197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3698,34 +3698,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1365</v>
+        <v>105930</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571098</v>
+        <v>571156</v>
       </c>
       <c r="R31" t="n">
-        <v>7057570</v>
+        <v>7057504</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,19 +3755,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3782,22 +3772,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129100194</v>
+        <v>129093045</v>
       </c>
       <c r="B32" t="n">
-        <v>5197</v>
+        <v>100820</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,34 +3795,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>105930</v>
+        <v>1365</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571156</v>
+        <v>571098</v>
       </c>
       <c r="R32" t="n">
-        <v>7057504</v>
+        <v>7057570</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,9 +3852,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3879,12 +3879,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3894,7 +3894,7 @@
         <v>129096206</v>
       </c>
       <c r="B33" t="n">
-        <v>96775</v>
+        <v>96778</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>129100195</v>
       </c>
       <c r="B35" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,32 +4187,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129096204</v>
+        <v>129100197</v>
       </c>
       <c r="B36" t="n">
-        <v>96775</v>
+        <v>57723</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4222,13 +4222,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>570894</v>
+        <v>570944</v>
       </c>
       <c r="R36" t="n">
-        <v>7057432</v>
+        <v>7057538</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4258,6 +4258,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4272,12 +4277,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4287,7 +4292,7 @@
         <v>129100213</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4381,32 +4386,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129100197</v>
+        <v>129096204</v>
       </c>
       <c r="B38" t="n">
-        <v>57723</v>
+        <v>96778</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4416,13 +4421,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>570944</v>
+        <v>570894</v>
       </c>
       <c r="R38" t="n">
-        <v>7057538</v>
+        <v>7057432</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4452,11 +4457,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4471,12 +4471,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4486,7 +4486,7 @@
         <v>129092519</v>
       </c>
       <c r="B39" t="n">
-        <v>100817</v>
+        <v>100820</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129094000</v>
+        <v>129094090</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +890,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570947</v>
+        <v>571144</v>
       </c>
       <c r="R4" t="n">
-        <v>7057312</v>
+        <v>7057314</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,19 +979,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129094153</v>
+        <v>129094000</v>
       </c>
       <c r="B5" t="n">
         <v>79035</v>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571029</v>
+        <v>570947</v>
       </c>
       <c r="R5" t="n">
-        <v>7057276</v>
+        <v>7057312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129094090</v>
+        <v>129094153</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,39 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571144</v>
+        <v>571029</v>
       </c>
       <c r="R6" t="n">
-        <v>7057314</v>
+        <v>7057276</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,12 +1193,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1511,51 +1511,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129096203</v>
+        <v>129091918</v>
       </c>
       <c r="B10" t="n">
-        <v>92855</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571163</v>
+        <v>571079</v>
       </c>
       <c r="R10" t="n">
-        <v>7057607</v>
+        <v>7057562</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1582,65 +1579,77 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129100200</v>
+        <v>129096203</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>92855</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ramariset, Ång</t>
@@ -1650,10 +1659,10 @@
         <v>571163</v>
       </c>
       <c r="R11" t="n">
-        <v>7057489</v>
+        <v>7057607</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1691,28 +1700,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129091918</v>
+        <v>129100200</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1720,34 +1730,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571079</v>
+        <v>571163</v>
       </c>
       <c r="R12" t="n">
-        <v>7057562</v>
+        <v>7057489</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,19 +1787,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1804,12 +1804,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2963,10 +2963,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129100202</v>
+        <v>129100212</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>91522</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,21 +2974,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571055</v>
+        <v>570991</v>
       </c>
       <c r="R24" t="n">
-        <v>7057572</v>
+        <v>7057492</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3034,11 +3034,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3065,10 +3060,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129100212</v>
+        <v>129100202</v>
       </c>
       <c r="B25" t="n">
-        <v>91522</v>
+        <v>57720</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3076,21 +3071,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3100,10 +3095,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>570991</v>
+        <v>571055</v>
       </c>
       <c r="R25" t="n">
-        <v>7057492</v>
+        <v>7057572</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3136,6 +3131,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3483,10 +3483,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129100204</v>
+        <v>129092361</v>
       </c>
       <c r="B29" t="n">
-        <v>80168</v>
+        <v>96778</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3494,34 +3494,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>2869</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>570947</v>
+        <v>571258</v>
       </c>
       <c r="R29" t="n">
-        <v>7057532</v>
+        <v>7057527</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,9 +3551,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3568,22 +3578,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129092361</v>
+        <v>129100204</v>
       </c>
       <c r="B30" t="n">
-        <v>96778</v>
+        <v>80168</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3591,34 +3601,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2869</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571258</v>
+        <v>570947</v>
       </c>
       <c r="R30" t="n">
-        <v>7057527</v>
+        <v>7057532</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,19 +3658,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3675,22 +3675,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129100194</v>
+        <v>129093045</v>
       </c>
       <c r="B31" t="n">
-        <v>5197</v>
+        <v>100820</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3698,34 +3698,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>105930</v>
+        <v>1365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571156</v>
+        <v>571098</v>
       </c>
       <c r="R31" t="n">
-        <v>7057504</v>
+        <v>7057570</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,9 +3755,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3772,22 +3782,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129093045</v>
+        <v>129096206</v>
       </c>
       <c r="B32" t="n">
-        <v>100820</v>
+        <v>96778</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3795,37 +3805,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571098</v>
+        <v>571159</v>
       </c>
       <c r="R32" t="n">
-        <v>7057570</v>
+        <v>7057565</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3852,19 +3862,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3879,22 +3879,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129096206</v>
+        <v>129100194</v>
       </c>
       <c r="B33" t="n">
-        <v>96778</v>
+        <v>5197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2869</v>
+        <v>105930</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3926,13 +3926,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571159</v>
+        <v>571156</v>
       </c>
       <c r="R33" t="n">
-        <v>7057565</v>
+        <v>7057504</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3976,12 +3976,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4187,10 +4187,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129100197</v>
+        <v>129100213</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4198,21 +4198,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>570944</v>
+        <v>570948</v>
       </c>
       <c r="R36" t="n">
-        <v>7057538</v>
+        <v>7057486</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4258,11 +4258,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4289,10 +4284,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129100213</v>
+        <v>129100197</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4300,21 +4295,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4324,10 +4319,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570948</v>
+        <v>570944</v>
       </c>
       <c r="R37" t="n">
-        <v>7057486</v>
+        <v>7057538</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4360,6 +4355,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -1511,48 +1511,51 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129091918</v>
+        <v>129096203</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>92855</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571079</v>
+        <v>571163</v>
       </c>
       <c r="R10" t="n">
-        <v>7057562</v>
+        <v>7057607</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1579,90 +1582,78 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129096203</v>
+        <v>129091918</v>
       </c>
       <c r="B11" t="n">
-        <v>92855</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571163</v>
+        <v>571079</v>
       </c>
       <c r="R11" t="n">
-        <v>7057607</v>
+        <v>7057562</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1689,30 +1680,39 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -3483,10 +3483,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129092361</v>
+        <v>129100204</v>
       </c>
       <c r="B29" t="n">
-        <v>96778</v>
+        <v>80168</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3494,34 +3494,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2869</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571258</v>
+        <v>570947</v>
       </c>
       <c r="R29" t="n">
-        <v>7057527</v>
+        <v>7057532</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,19 +3551,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3578,22 +3568,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129100204</v>
+        <v>129092361</v>
       </c>
       <c r="B30" t="n">
-        <v>80168</v>
+        <v>96778</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3601,34 +3591,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>2869</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>570947</v>
+        <v>571258</v>
       </c>
       <c r="R30" t="n">
-        <v>7057532</v>
+        <v>7057527</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,9 +3648,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3675,12 +3675,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129094090</v>
+        <v>129094000</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571144</v>
+        <v>570947</v>
       </c>
       <c r="R4" t="n">
-        <v>7057314</v>
+        <v>7057312</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +949,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +959,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,19 +974,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129094000</v>
+        <v>129094153</v>
       </c>
       <c r="B5" t="n">
         <v>79035</v>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570947</v>
+        <v>571029</v>
       </c>
       <c r="R5" t="n">
-        <v>7057312</v>
+        <v>7057276</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129094153</v>
+        <v>129094090</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,34 +1104,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571029</v>
+        <v>571144</v>
       </c>
       <c r="R6" t="n">
-        <v>7057276</v>
+        <v>7057314</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,12 +1193,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1511,38 +1511,35 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129096203</v>
+        <v>129100200</v>
       </c>
       <c r="B10" t="n">
-        <v>92855</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramariset, Ång</t>
@@ -1552,10 +1549,10 @@
         <v>571163</v>
       </c>
       <c r="R10" t="n">
-        <v>7057607</v>
+        <v>7057489</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,19 +1590,18 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1719,35 +1715,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129100200</v>
+        <v>129096203</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>92855</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ramariset, Ång</t>
@@ -1757,10 +1756,10 @@
         <v>571163</v>
       </c>
       <c r="R12" t="n">
-        <v>7057489</v>
+        <v>7057607</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1798,18 +1797,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129096197</v>
+        <v>129092795</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,37 +2357,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570925</v>
+        <v>571218</v>
       </c>
       <c r="R18" t="n">
-        <v>7057499</v>
+        <v>7057576</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2414,9 +2419,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2431,22 +2446,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129092795</v>
+        <v>129096197</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,42 +2469,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571218</v>
+        <v>570925</v>
       </c>
       <c r="R19" t="n">
-        <v>7057576</v>
+        <v>7057499</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2516,19 +2526,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2543,12 +2543,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3259,45 +3259,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129093842</v>
+        <v>129091441</v>
       </c>
       <c r="B27" t="n">
-        <v>91491</v>
+        <v>57723</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>570896</v>
+        <v>570938</v>
       </c>
       <c r="R27" t="n">
-        <v>7057451</v>
+        <v>7057605</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3329,7 +3334,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3339,7 +3344,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3366,50 +3376,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129091441</v>
+        <v>129093842</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>91491</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>570938</v>
+        <v>570896</v>
       </c>
       <c r="R28" t="n">
-        <v>7057605</v>
+        <v>7057451</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3441,7 +3446,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3451,12 +3456,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3483,10 +3483,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129100204</v>
+        <v>129092361</v>
       </c>
       <c r="B29" t="n">
-        <v>80168</v>
+        <v>96778</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3494,34 +3494,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>2869</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>570947</v>
+        <v>571258</v>
       </c>
       <c r="R29" t="n">
-        <v>7057532</v>
+        <v>7057527</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,9 +3551,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3568,22 +3578,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129092361</v>
+        <v>129100204</v>
       </c>
       <c r="B30" t="n">
-        <v>96778</v>
+        <v>80168</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3591,34 +3601,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2869</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571258</v>
+        <v>570947</v>
       </c>
       <c r="R30" t="n">
-        <v>7057527</v>
+        <v>7057532</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,19 +3658,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3675,22 +3675,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129093045</v>
+        <v>129096206</v>
       </c>
       <c r="B31" t="n">
-        <v>100820</v>
+        <v>96778</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3698,37 +3698,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571098</v>
+        <v>571159</v>
       </c>
       <c r="R31" t="n">
-        <v>7057570</v>
+        <v>7057565</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3755,19 +3755,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3782,22 +3772,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129096206</v>
+        <v>129093045</v>
       </c>
       <c r="B32" t="n">
-        <v>96778</v>
+        <v>100820</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,37 +3795,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571159</v>
+        <v>571098</v>
       </c>
       <c r="R32" t="n">
-        <v>7057565</v>
+        <v>7057570</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3862,9 +3852,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3879,12 +3879,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129093948</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129100217</v>
       </c>
       <c r="B3" t="n">
-        <v>96778</v>
+        <v>96788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129094000</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129094153</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129094090</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129096194</v>
       </c>
       <c r="B7" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>129093962</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>129100196</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129100200</v>
+        <v>129091918</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,34 +1522,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571163</v>
+        <v>571079</v>
       </c>
       <c r="R10" t="n">
-        <v>7057489</v>
+        <v>7057562</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,9 +1579,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,60 +1606,63 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129091918</v>
+        <v>129096203</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>92862</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571079</v>
+        <v>571163</v>
       </c>
       <c r="R11" t="n">
-        <v>7057562</v>
+        <v>7057607</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1676,77 +1689,65 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129096203</v>
+        <v>129100200</v>
       </c>
       <c r="B12" t="n">
-        <v>92855</v>
+        <v>57885</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ramariset, Ång</t>
@@ -1756,10 +1757,10 @@
         <v>571163</v>
       </c>
       <c r="R12" t="n">
-        <v>7057607</v>
+        <v>7057489</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1797,19 +1798,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1819,7 +1819,7 @@
         <v>129100218</v>
       </c>
       <c r="B13" t="n">
-        <v>96778</v>
+        <v>96788</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>129100211</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>129091516</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>129092344</v>
       </c>
       <c r="B16" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>129093213</v>
       </c>
       <c r="B17" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129092795</v>
+        <v>129096197</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,42 +2357,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571218</v>
+        <v>570925</v>
       </c>
       <c r="R18" t="n">
-        <v>7057576</v>
+        <v>7057499</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2419,19 +2414,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2446,22 +2431,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129096197</v>
+        <v>129092795</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,37 +2454,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570925</v>
+        <v>571218</v>
       </c>
       <c r="R19" t="n">
-        <v>7057499</v>
+        <v>7057576</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2526,9 +2516,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2543,12 +2543,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2558,7 +2558,7 @@
         <v>129100214</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>129096205</v>
       </c>
       <c r="B21" t="n">
-        <v>96778</v>
+        <v>96788</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>129100203</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>129091908</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>129100212</v>
       </c>
       <c r="B24" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>129100202</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>129096198</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>129091441</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>129093842</v>
       </c>
       <c r="B28" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>129092361</v>
       </c>
       <c r="B29" t="n">
-        <v>96778</v>
+        <v>96788</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>129100204</v>
       </c>
       <c r="B30" t="n">
-        <v>80168</v>
+        <v>80172</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3687,10 +3687,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129096206</v>
+        <v>129093045</v>
       </c>
       <c r="B31" t="n">
-        <v>96778</v>
+        <v>100830</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3698,37 +3698,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571159</v>
+        <v>571098</v>
       </c>
       <c r="R31" t="n">
-        <v>7057565</v>
+        <v>7057570</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3755,9 +3755,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3772,22 +3782,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129093045</v>
+        <v>129096206</v>
       </c>
       <c r="B32" t="n">
-        <v>100820</v>
+        <v>96788</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3795,37 +3805,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571098</v>
+        <v>571159</v>
       </c>
       <c r="R32" t="n">
-        <v>7057570</v>
+        <v>7057565</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3852,19 +3862,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3879,12 +3879,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3991,7 +3991,7 @@
         <v>129100201</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>129100195</v>
       </c>
       <c r="B35" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,32 +4187,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129100213</v>
+        <v>129096204</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>96788</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4222,13 +4222,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>570948</v>
+        <v>570894</v>
       </c>
       <c r="R36" t="n">
-        <v>7057486</v>
+        <v>7057432</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4272,22 +4272,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129100197</v>
+        <v>129100213</v>
       </c>
       <c r="B37" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4295,21 +4295,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570944</v>
+        <v>570948</v>
       </c>
       <c r="R37" t="n">
-        <v>7057538</v>
+        <v>7057486</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4355,11 +4355,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4386,32 +4381,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096204</v>
+        <v>129100197</v>
       </c>
       <c r="B38" t="n">
-        <v>96778</v>
+        <v>57725</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4421,13 +4416,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>570894</v>
+        <v>570944</v>
       </c>
       <c r="R38" t="n">
-        <v>7057432</v>
+        <v>7057538</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4457,6 +4452,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4471,57 +4471,62 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129092519</v>
+        <v>129091900</v>
       </c>
       <c r="B39" t="n">
-        <v>100820</v>
+        <v>57725</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571253</v>
+        <v>571175</v>
       </c>
       <c r="R39" t="n">
-        <v>7057540</v>
+        <v>7057492</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4553,7 +4558,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4563,7 +4568,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4590,50 +4600,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129091900</v>
+        <v>129092519</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>100830</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571175</v>
+        <v>571253</v>
       </c>
       <c r="R40" t="n">
-        <v>7057492</v>
+        <v>7057540</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4665,7 +4670,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4675,12 +4680,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -4483,50 +4483,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129091900</v>
+        <v>129092519</v>
       </c>
       <c r="B39" t="n">
-        <v>57725</v>
+        <v>100830</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571175</v>
+        <v>571253</v>
       </c>
       <c r="R39" t="n">
-        <v>7057492</v>
+        <v>7057540</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4558,7 +4553,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4568,12 +4563,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4600,45 +4590,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129092519</v>
+        <v>129091900</v>
       </c>
       <c r="B40" t="n">
-        <v>100830</v>
+        <v>57725</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571253</v>
+        <v>571175</v>
       </c>
       <c r="R40" t="n">
-        <v>7057540</v>
+        <v>7057492</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4670,7 +4665,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4680,7 +4675,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129100217</v>
       </c>
       <c r="B3" t="n">
-        <v>96788</v>
+        <v>96795</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129094000</v>
+        <v>129094153</v>
       </c>
       <c r="B4" t="n">
         <v>79039</v>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570947</v>
+        <v>571029</v>
       </c>
       <c r="R4" t="n">
-        <v>7057312</v>
+        <v>7057276</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129094153</v>
+        <v>129094000</v>
       </c>
       <c r="B5" t="n">
         <v>79039</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571029</v>
+        <v>570947</v>
       </c>
       <c r="R5" t="n">
-        <v>7057276</v>
+        <v>7057312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1208,7 +1208,7 @@
         <v>129096194</v>
       </c>
       <c r="B7" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129091918</v>
+        <v>129100200</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>57885</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,34 +1522,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571079</v>
+        <v>571163</v>
       </c>
       <c r="R10" t="n">
-        <v>7057562</v>
+        <v>7057489</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,19 +1579,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1606,12 +1596,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1621,7 +1611,7 @@
         <v>129096203</v>
       </c>
       <c r="B11" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1719,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129100200</v>
+        <v>129091918</v>
       </c>
       <c r="B12" t="n">
-        <v>57885</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,34 +1720,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571163</v>
+        <v>571079</v>
       </c>
       <c r="R12" t="n">
-        <v>7057489</v>
+        <v>7057562</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,9 +1777,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1804,12 +1804,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1819,7 +1819,7 @@
         <v>129100218</v>
       </c>
       <c r="B13" t="n">
-        <v>96788</v>
+        <v>96795</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>129100211</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>129092344</v>
       </c>
       <c r="B16" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2652,32 +2652,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129096205</v>
+        <v>129100203</v>
       </c>
       <c r="B21" t="n">
-        <v>96788</v>
+        <v>57722</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2687,13 +2687,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570898</v>
+        <v>570968</v>
       </c>
       <c r="R21" t="n">
-        <v>7057466</v>
+        <v>7057538</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2723,6 +2723,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2737,44 +2742,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129100203</v>
+        <v>129096205</v>
       </c>
       <c r="B22" t="n">
-        <v>57722</v>
+        <v>96795</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2784,13 +2789,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570968</v>
+        <v>570898</v>
       </c>
       <c r="R22" t="n">
-        <v>7057538</v>
+        <v>7057466</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2820,11 +2825,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2839,12 +2839,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2963,10 +2963,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129100212</v>
+        <v>129100202</v>
       </c>
       <c r="B24" t="n">
-        <v>91529</v>
+        <v>57722</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,21 +2974,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>570991</v>
+        <v>571055</v>
       </c>
       <c r="R24" t="n">
-        <v>7057492</v>
+        <v>7057572</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3034,6 +3034,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3060,10 +3065,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129100202</v>
+        <v>129100212</v>
       </c>
       <c r="B25" t="n">
-        <v>57722</v>
+        <v>91536</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,21 +3076,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3095,10 +3100,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571055</v>
+        <v>570991</v>
       </c>
       <c r="R25" t="n">
-        <v>7057572</v>
+        <v>7057492</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3131,11 +3136,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3259,50 +3259,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129091441</v>
+        <v>129093842</v>
       </c>
       <c r="B27" t="n">
-        <v>57725</v>
+        <v>91504</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>570938</v>
+        <v>570896</v>
       </c>
       <c r="R27" t="n">
-        <v>7057605</v>
+        <v>7057451</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3334,7 +3329,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3344,12 +3339,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3376,45 +3366,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129093842</v>
+        <v>129091441</v>
       </c>
       <c r="B28" t="n">
-        <v>91497</v>
+        <v>57725</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>570896</v>
+        <v>570938</v>
       </c>
       <c r="R28" t="n">
-        <v>7057451</v>
+        <v>7057605</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3446,7 +3441,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3456,7 +3451,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3483,10 +3483,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129092361</v>
+        <v>129100204</v>
       </c>
       <c r="B29" t="n">
-        <v>96788</v>
+        <v>80172</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3494,34 +3494,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2869</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571258</v>
+        <v>570947</v>
       </c>
       <c r="R29" t="n">
-        <v>7057527</v>
+        <v>7057532</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,19 +3551,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3578,22 +3568,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129100204</v>
+        <v>129092361</v>
       </c>
       <c r="B30" t="n">
-        <v>80172</v>
+        <v>96795</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3601,34 +3591,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>2869</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>570947</v>
+        <v>571258</v>
       </c>
       <c r="R30" t="n">
-        <v>7057532</v>
+        <v>7057527</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,9 +3648,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3675,12 +3675,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3690,7 +3690,7 @@
         <v>129093045</v>
       </c>
       <c r="B31" t="n">
-        <v>100830</v>
+        <v>100837</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129096206</v>
+        <v>129100194</v>
       </c>
       <c r="B32" t="n">
-        <v>96788</v>
+        <v>5197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2869</v>
+        <v>105930</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3829,13 +3829,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571159</v>
+        <v>571156</v>
       </c>
       <c r="R32" t="n">
-        <v>7057565</v>
+        <v>7057504</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3879,22 +3879,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129100194</v>
+        <v>129096206</v>
       </c>
       <c r="B33" t="n">
-        <v>5197</v>
+        <v>96795</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105930</v>
+        <v>2869</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3926,13 +3926,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571156</v>
+        <v>571159</v>
       </c>
       <c r="R33" t="n">
-        <v>7057504</v>
+        <v>7057565</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3976,12 +3976,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4093,7 +4093,7 @@
         <v>129100195</v>
       </c>
       <c r="B35" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,32 +4187,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129096204</v>
+        <v>129100197</v>
       </c>
       <c r="B36" t="n">
-        <v>96788</v>
+        <v>57725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4222,13 +4222,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>570894</v>
+        <v>570944</v>
       </c>
       <c r="R36" t="n">
-        <v>7057432</v>
+        <v>7057538</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4258,6 +4258,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4272,44 +4277,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129100213</v>
+        <v>129096204</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>96795</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4319,13 +4324,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570948</v>
+        <v>570894</v>
       </c>
       <c r="R37" t="n">
-        <v>7057486</v>
+        <v>7057432</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4369,22 +4374,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129100197</v>
+        <v>129100213</v>
       </c>
       <c r="B38" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4392,21 +4397,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4416,10 +4421,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>570944</v>
+        <v>570948</v>
       </c>
       <c r="R38" t="n">
-        <v>7057538</v>
+        <v>7057486</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4452,11 +4457,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4486,7 +4486,7 @@
         <v>129092519</v>
       </c>
       <c r="B39" t="n">
-        <v>100830</v>
+        <v>100837</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129093948</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129100217</v>
       </c>
       <c r="B3" t="n">
-        <v>96795</v>
+        <v>96797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129094153</v>
+        <v>129094090</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +890,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571029</v>
+        <v>571144</v>
       </c>
       <c r="R4" t="n">
-        <v>7057276</v>
+        <v>7057314</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -989,7 +994,7 @@
         <v>129094000</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129094090</v>
+        <v>129094153</v>
       </c>
       <c r="B6" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,39 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571144</v>
+        <v>571029</v>
       </c>
       <c r="R6" t="n">
-        <v>7057314</v>
+        <v>7057276</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,12 +1193,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1208,7 +1208,7 @@
         <v>129096194</v>
       </c>
       <c r="B7" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>129093962</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>129100196</v>
       </c>
       <c r="B9" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129100200</v>
+        <v>129091918</v>
       </c>
       <c r="B10" t="n">
-        <v>57885</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,34 +1522,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571163</v>
+        <v>571079</v>
       </c>
       <c r="R10" t="n">
-        <v>7057489</v>
+        <v>7057562</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,9 +1579,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,50 +1606,47 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129096203</v>
+        <v>129100200</v>
       </c>
       <c r="B11" t="n">
-        <v>92869</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ramariset, Ång</t>
@@ -1649,10 +1656,10 @@
         <v>571163</v>
       </c>
       <c r="R11" t="n">
-        <v>7057607</v>
+        <v>7057489</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1690,67 +1697,69 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129091918</v>
+        <v>129096203</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>92871</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571079</v>
+        <v>571163</v>
       </c>
       <c r="R12" t="n">
-        <v>7057562</v>
+        <v>7057607</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1777,39 +1786,30 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1819,7 +1819,7 @@
         <v>129100218</v>
       </c>
       <c r="B13" t="n">
-        <v>96795</v>
+        <v>96797</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>129100211</v>
       </c>
       <c r="B14" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>129091516</v>
       </c>
       <c r="B15" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129092344</v>
+        <v>129093213</v>
       </c>
       <c r="B16" t="n">
-        <v>91558</v>
+        <v>80146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,21 +2143,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571249</v>
+        <v>570967</v>
       </c>
       <c r="R16" t="n">
-        <v>7057525</v>
+        <v>7057481</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2227,22 +2227,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129093213</v>
+        <v>129092344</v>
       </c>
       <c r="B17" t="n">
-        <v>80144</v>
+        <v>91560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,21 +2250,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570967</v>
+        <v>571249</v>
       </c>
       <c r="R17" t="n">
-        <v>7057481</v>
+        <v>7057525</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2334,12 +2334,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2349,7 +2349,7 @@
         <v>129096197</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>129092795</v>
       </c>
       <c r="B19" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>129100214</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>129100203</v>
       </c>
       <c r="B21" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>129096205</v>
       </c>
       <c r="B22" t="n">
-        <v>96795</v>
+        <v>96797</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>129091908</v>
       </c>
       <c r="B23" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,10 +2963,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129100202</v>
+        <v>129100212</v>
       </c>
       <c r="B24" t="n">
-        <v>57722</v>
+        <v>91538</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,21 +2974,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571055</v>
+        <v>570991</v>
       </c>
       <c r="R24" t="n">
-        <v>7057572</v>
+        <v>7057492</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3034,11 +3034,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3065,10 +3060,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129100212</v>
+        <v>129100202</v>
       </c>
       <c r="B25" t="n">
-        <v>91536</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3076,21 +3071,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3100,10 +3095,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>570991</v>
+        <v>571055</v>
       </c>
       <c r="R25" t="n">
-        <v>7057492</v>
+        <v>7057572</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3136,6 +3131,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3165,7 +3165,7 @@
         <v>129096198</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3259,45 +3259,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129093842</v>
+        <v>129091441</v>
       </c>
       <c r="B27" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>570896</v>
+        <v>570938</v>
       </c>
       <c r="R27" t="n">
-        <v>7057451</v>
+        <v>7057605</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3329,7 +3334,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3339,7 +3344,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3366,50 +3376,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129091441</v>
+        <v>129093842</v>
       </c>
       <c r="B28" t="n">
-        <v>57725</v>
+        <v>91506</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>570938</v>
+        <v>570896</v>
       </c>
       <c r="R28" t="n">
-        <v>7057605</v>
+        <v>7057451</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3441,7 +3446,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3451,12 +3456,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3483,10 +3483,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129100204</v>
+        <v>129092361</v>
       </c>
       <c r="B29" t="n">
-        <v>80172</v>
+        <v>96797</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3494,34 +3494,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>2869</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>570947</v>
+        <v>571258</v>
       </c>
       <c r="R29" t="n">
-        <v>7057532</v>
+        <v>7057527</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,9 +3551,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3568,22 +3578,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129092361</v>
+        <v>129100204</v>
       </c>
       <c r="B30" t="n">
-        <v>96795</v>
+        <v>80174</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3591,34 +3601,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2869</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571258</v>
+        <v>570947</v>
       </c>
       <c r="R30" t="n">
-        <v>7057527</v>
+        <v>7057532</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,19 +3658,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3675,22 +3675,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129093045</v>
+        <v>129100194</v>
       </c>
       <c r="B31" t="n">
-        <v>100837</v>
+        <v>5197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3698,34 +3698,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1365</v>
+        <v>105930</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571098</v>
+        <v>571156</v>
       </c>
       <c r="R31" t="n">
-        <v>7057570</v>
+        <v>7057504</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,19 +3755,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3782,22 +3772,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129100194</v>
+        <v>129093045</v>
       </c>
       <c r="B32" t="n">
-        <v>5197</v>
+        <v>100839</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,34 +3795,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>105930</v>
+        <v>1365</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571156</v>
+        <v>571098</v>
       </c>
       <c r="R32" t="n">
-        <v>7057504</v>
+        <v>7057570</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,9 +3852,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3879,12 +3879,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3894,7 +3894,7 @@
         <v>129096206</v>
       </c>
       <c r="B33" t="n">
-        <v>96795</v>
+        <v>96797</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>129100201</v>
       </c>
       <c r="B34" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>129100195</v>
       </c>
       <c r="B35" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,32 +4187,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129100197</v>
+        <v>129096204</v>
       </c>
       <c r="B36" t="n">
-        <v>57725</v>
+        <v>96797</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4222,13 +4222,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>570944</v>
+        <v>570894</v>
       </c>
       <c r="R36" t="n">
-        <v>7057538</v>
+        <v>7057432</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4258,11 +4258,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4277,44 +4272,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129096204</v>
+        <v>129100213</v>
       </c>
       <c r="B37" t="n">
-        <v>96795</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4324,13 +4319,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570894</v>
+        <v>570948</v>
       </c>
       <c r="R37" t="n">
-        <v>7057432</v>
+        <v>7057486</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4374,22 +4369,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129100213</v>
+        <v>129100197</v>
       </c>
       <c r="B38" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4397,21 +4392,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4421,10 +4416,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>570948</v>
+        <v>570944</v>
       </c>
       <c r="R38" t="n">
-        <v>7057486</v>
+        <v>7057538</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4457,6 +4452,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4486,7 +4486,7 @@
         <v>129092519</v>
       </c>
       <c r="B39" t="n">
-        <v>100837</v>
+        <v>100839</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>129091900</v>
       </c>
       <c r="B40" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129094090</v>
+        <v>129094000</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571144</v>
+        <v>570947</v>
       </c>
       <c r="R4" t="n">
-        <v>7057314</v>
+        <v>7057312</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +949,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +959,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,19 +974,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129094000</v>
+        <v>129094153</v>
       </c>
       <c r="B5" t="n">
         <v>79041</v>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570947</v>
+        <v>571029</v>
       </c>
       <c r="R5" t="n">
-        <v>7057312</v>
+        <v>7057276</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129094153</v>
+        <v>129094090</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,34 +1104,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571029</v>
+        <v>571144</v>
       </c>
       <c r="R6" t="n">
-        <v>7057276</v>
+        <v>7057314</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,12 +1193,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1511,48 +1511,51 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129091918</v>
+        <v>129096203</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>92871</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571079</v>
+        <v>571163</v>
       </c>
       <c r="R10" t="n">
-        <v>7057562</v>
+        <v>7057607</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1579,49 +1582,40 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129100200</v>
+        <v>129091918</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,34 +1623,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571163</v>
+        <v>571079</v>
       </c>
       <c r="R11" t="n">
-        <v>7057489</v>
+        <v>7057562</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,9 +1680,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,50 +1707,47 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129096203</v>
+        <v>129100200</v>
       </c>
       <c r="B12" t="n">
-        <v>92871</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ramariset, Ång</t>
@@ -1756,10 +1757,10 @@
         <v>571163</v>
       </c>
       <c r="R12" t="n">
-        <v>7057607</v>
+        <v>7057489</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1797,19 +1798,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129096197</v>
+        <v>129092795</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,37 +2357,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570925</v>
+        <v>571218</v>
       </c>
       <c r="R18" t="n">
-        <v>7057499</v>
+        <v>7057576</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2414,9 +2419,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2431,22 +2446,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129092795</v>
+        <v>129096197</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,42 +2469,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571218</v>
+        <v>570925</v>
       </c>
       <c r="R19" t="n">
-        <v>7057576</v>
+        <v>7057499</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2516,19 +2526,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2543,12 +2543,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2652,32 +2652,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129100203</v>
+        <v>129096205</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>96797</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2687,13 +2687,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570968</v>
+        <v>570898</v>
       </c>
       <c r="R21" t="n">
-        <v>7057538</v>
+        <v>7057466</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2723,11 +2723,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2742,44 +2737,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129096205</v>
+        <v>129100203</v>
       </c>
       <c r="B22" t="n">
-        <v>96797</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2789,13 +2784,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570898</v>
+        <v>570968</v>
       </c>
       <c r="R22" t="n">
-        <v>7057466</v>
+        <v>7057538</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2825,6 +2820,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2839,12 +2839,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129093045</v>
+        <v>129096206</v>
       </c>
       <c r="B32" t="n">
-        <v>100839</v>
+        <v>96797</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3795,37 +3795,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571098</v>
+        <v>571159</v>
       </c>
       <c r="R32" t="n">
-        <v>7057570</v>
+        <v>7057565</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3852,19 +3852,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3879,22 +3869,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129096206</v>
+        <v>129093045</v>
       </c>
       <c r="B33" t="n">
-        <v>96797</v>
+        <v>100839</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,37 +3892,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571159</v>
+        <v>571098</v>
       </c>
       <c r="R33" t="n">
-        <v>7057565</v>
+        <v>7057570</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3959,9 +3949,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3976,12 +3976,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4187,32 +4187,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129096204</v>
+        <v>129100213</v>
       </c>
       <c r="B36" t="n">
-        <v>96797</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4222,13 +4222,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>570894</v>
+        <v>570948</v>
       </c>
       <c r="R36" t="n">
-        <v>7057432</v>
+        <v>7057486</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4272,22 +4272,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129100213</v>
+        <v>129100197</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4295,21 +4295,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570948</v>
+        <v>570944</v>
       </c>
       <c r="R37" t="n">
-        <v>7057486</v>
+        <v>7057538</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4355,6 +4355,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4381,32 +4386,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129100197</v>
+        <v>129096204</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>96797</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4416,13 +4421,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>570944</v>
+        <v>570894</v>
       </c>
       <c r="R38" t="n">
-        <v>7057538</v>
+        <v>7057432</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4452,11 +4457,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4471,12 +4471,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129094000</v>
+        <v>129094090</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +890,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570947</v>
+        <v>571144</v>
       </c>
       <c r="R4" t="n">
-        <v>7057312</v>
+        <v>7057314</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,19 +979,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129094153</v>
+        <v>129094000</v>
       </c>
       <c r="B5" t="n">
         <v>79041</v>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571029</v>
+        <v>570947</v>
       </c>
       <c r="R5" t="n">
-        <v>7057276</v>
+        <v>7057312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129094090</v>
+        <v>129094153</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,39 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571144</v>
+        <v>571029</v>
       </c>
       <c r="R6" t="n">
-        <v>7057314</v>
+        <v>7057276</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,12 +1193,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1511,38 +1511,35 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129096203</v>
+        <v>129100200</v>
       </c>
       <c r="B10" t="n">
-        <v>92871</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramariset, Ång</t>
@@ -1552,10 +1549,10 @@
         <v>571163</v>
       </c>
       <c r="R10" t="n">
-        <v>7057607</v>
+        <v>7057489</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,67 +1590,69 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129091918</v>
+        <v>129096203</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>92871</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571079</v>
+        <v>571163</v>
       </c>
       <c r="R11" t="n">
-        <v>7057562</v>
+        <v>7057607</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1680,49 +1679,40 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129100200</v>
+        <v>129091918</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,34 +1720,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571163</v>
+        <v>571079</v>
       </c>
       <c r="R12" t="n">
-        <v>7057489</v>
+        <v>7057562</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,9 +1777,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1804,12 +1804,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -3259,50 +3259,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129091441</v>
+        <v>129093842</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>91506</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>570938</v>
+        <v>570896</v>
       </c>
       <c r="R27" t="n">
-        <v>7057605</v>
+        <v>7057451</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3334,7 +3329,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3344,12 +3339,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3376,45 +3366,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129093842</v>
+        <v>129091441</v>
       </c>
       <c r="B28" t="n">
-        <v>91506</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>570896</v>
+        <v>570938</v>
       </c>
       <c r="R28" t="n">
-        <v>7057451</v>
+        <v>7057605</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3446,7 +3441,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3456,7 +3451,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3687,10 +3687,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129100194</v>
+        <v>129093045</v>
       </c>
       <c r="B31" t="n">
-        <v>5197</v>
+        <v>100839</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3698,34 +3698,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>105930</v>
+        <v>1365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571156</v>
+        <v>571098</v>
       </c>
       <c r="R31" t="n">
-        <v>7057504</v>
+        <v>7057570</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,9 +3755,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3772,12 +3782,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3881,10 +3891,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129093045</v>
+        <v>129100194</v>
       </c>
       <c r="B33" t="n">
-        <v>100839</v>
+        <v>5197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3892,34 +3902,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1365</v>
+        <v>105930</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571098</v>
+        <v>571156</v>
       </c>
       <c r="R33" t="n">
-        <v>7057570</v>
+        <v>7057504</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,19 +3959,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3976,12 +3976,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4187,32 +4187,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129100213</v>
+        <v>129096204</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>96797</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4222,13 +4222,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>570948</v>
+        <v>570894</v>
       </c>
       <c r="R36" t="n">
-        <v>7057486</v>
+        <v>7057432</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4272,22 +4272,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129100197</v>
+        <v>129100213</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4295,21 +4295,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570944</v>
+        <v>570948</v>
       </c>
       <c r="R37" t="n">
-        <v>7057538</v>
+        <v>7057486</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4355,11 +4355,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4386,32 +4381,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096204</v>
+        <v>129100197</v>
       </c>
       <c r="B38" t="n">
-        <v>96797</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4421,13 +4416,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>570894</v>
+        <v>570944</v>
       </c>
       <c r="R38" t="n">
-        <v>7057432</v>
+        <v>7057538</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4457,6 +4452,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4471,12 +4471,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129100217</v>
       </c>
       <c r="B3" t="n">
-        <v>96797</v>
+        <v>96823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129094090</v>
+        <v>129094000</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571144</v>
+        <v>570947</v>
       </c>
       <c r="R4" t="n">
-        <v>7057314</v>
+        <v>7057312</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +949,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +959,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,19 +974,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129094000</v>
+        <v>129094153</v>
       </c>
       <c r="B5" t="n">
         <v>79041</v>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570947</v>
+        <v>571029</v>
       </c>
       <c r="R5" t="n">
-        <v>7057312</v>
+        <v>7057276</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129094153</v>
+        <v>129094090</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,34 +1104,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571029</v>
+        <v>571144</v>
       </c>
       <c r="R6" t="n">
-        <v>7057276</v>
+        <v>7057314</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,12 +1193,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1208,7 +1208,7 @@
         <v>129096194</v>
       </c>
       <c r="B7" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1511,35 +1511,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129100200</v>
+        <v>129096203</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>92857</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramariset, Ång</t>
@@ -1549,10 +1552,10 @@
         <v>571163</v>
       </c>
       <c r="R10" t="n">
-        <v>7057489</v>
+        <v>7057607</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1590,69 +1593,67 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129096203</v>
+        <v>129091918</v>
       </c>
       <c r="B11" t="n">
-        <v>92871</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571163</v>
+        <v>571079</v>
       </c>
       <c r="R11" t="n">
-        <v>7057607</v>
+        <v>7057562</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1679,40 +1680,49 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129091918</v>
+        <v>129100200</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1720,34 +1730,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571079</v>
+        <v>571163</v>
       </c>
       <c r="R12" t="n">
-        <v>7057562</v>
+        <v>7057489</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,19 +1787,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1804,12 +1804,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1819,7 +1819,7 @@
         <v>129100218</v>
       </c>
       <c r="B13" t="n">
-        <v>96797</v>
+        <v>96823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>129100211</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>129092344</v>
       </c>
       <c r="B17" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129092795</v>
+        <v>129096197</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,42 +2357,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571218</v>
+        <v>570925</v>
       </c>
       <c r="R18" t="n">
-        <v>7057576</v>
+        <v>7057499</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2419,19 +2414,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2446,22 +2431,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129096197</v>
+        <v>129092795</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,37 +2454,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570925</v>
+        <v>571218</v>
       </c>
       <c r="R19" t="n">
-        <v>7057499</v>
+        <v>7057576</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2526,9 +2516,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2543,12 +2543,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2655,7 +2655,7 @@
         <v>129096205</v>
       </c>
       <c r="B21" t="n">
-        <v>96797</v>
+        <v>96823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>129100212</v>
       </c>
       <c r="B24" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>129093842</v>
       </c>
       <c r="B27" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3483,10 +3483,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129092361</v>
+        <v>129100204</v>
       </c>
       <c r="B29" t="n">
-        <v>96797</v>
+        <v>80174</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3494,34 +3494,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2869</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571258</v>
+        <v>570947</v>
       </c>
       <c r="R29" t="n">
-        <v>7057527</v>
+        <v>7057532</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,19 +3551,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3578,22 +3568,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129100204</v>
+        <v>129092361</v>
       </c>
       <c r="B30" t="n">
-        <v>80174</v>
+        <v>96823</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3601,34 +3591,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>2869</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>570947</v>
+        <v>571258</v>
       </c>
       <c r="R30" t="n">
-        <v>7057532</v>
+        <v>7057527</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,9 +3648,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3675,22 +3675,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129093045</v>
+        <v>129100194</v>
       </c>
       <c r="B31" t="n">
-        <v>100839</v>
+        <v>5197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3698,34 +3698,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1365</v>
+        <v>105930</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571098</v>
+        <v>571156</v>
       </c>
       <c r="R31" t="n">
-        <v>7057570</v>
+        <v>7057504</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,19 +3755,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3782,22 +3772,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129096206</v>
+        <v>129093045</v>
       </c>
       <c r="B32" t="n">
-        <v>96797</v>
+        <v>100865</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,37 +3795,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571159</v>
+        <v>571098</v>
       </c>
       <c r="R32" t="n">
-        <v>7057565</v>
+        <v>7057570</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3862,9 +3852,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3879,22 +3879,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129100194</v>
+        <v>129096206</v>
       </c>
       <c r="B33" t="n">
-        <v>5197</v>
+        <v>96823</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105930</v>
+        <v>2869</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3926,13 +3926,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571156</v>
+        <v>571159</v>
       </c>
       <c r="R33" t="n">
-        <v>7057504</v>
+        <v>7057565</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3976,12 +3976,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4093,7 +4093,7 @@
         <v>129100195</v>
       </c>
       <c r="B35" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,32 +4187,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129096204</v>
+        <v>129100213</v>
       </c>
       <c r="B36" t="n">
-        <v>96797</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4222,13 +4222,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>570894</v>
+        <v>570948</v>
       </c>
       <c r="R36" t="n">
-        <v>7057432</v>
+        <v>7057486</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4272,22 +4272,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129100213</v>
+        <v>129100197</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4295,21 +4295,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570948</v>
+        <v>570944</v>
       </c>
       <c r="R37" t="n">
-        <v>7057486</v>
+        <v>7057538</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4355,6 +4355,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4381,32 +4386,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129100197</v>
+        <v>129096204</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>96823</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4416,13 +4421,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>570944</v>
+        <v>570894</v>
       </c>
       <c r="R38" t="n">
-        <v>7057538</v>
+        <v>7057432</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4452,11 +4457,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4471,12 +4471,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4486,7 +4486,7 @@
         <v>129092519</v>
       </c>
       <c r="B39" t="n">
-        <v>100839</v>
+        <v>100865</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129100217</v>
       </c>
       <c r="B3" t="n">
-        <v>96823</v>
+        <v>96824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129096194</v>
       </c>
       <c r="B7" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>129096203</v>
       </c>
       <c r="B10" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>129100218</v>
       </c>
       <c r="B13" t="n">
-        <v>96823</v>
+        <v>96824</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>129100211</v>
       </c>
       <c r="B14" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129093213</v>
+        <v>129092344</v>
       </c>
       <c r="B16" t="n">
-        <v>80146</v>
+        <v>91560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,23 +2143,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2167,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570967</v>
+        <v>571249</v>
       </c>
       <c r="R16" t="n">
-        <v>7057481</v>
+        <v>7057525</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,7 +2198,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2212,7 +2208,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2227,22 +2223,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129092344</v>
+        <v>129093213</v>
       </c>
       <c r="B17" t="n">
-        <v>91558</v>
+        <v>80146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2274,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571249</v>
+        <v>570967</v>
       </c>
       <c r="R17" t="n">
-        <v>7057525</v>
+        <v>7057481</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2309,7 +2305,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2319,7 +2315,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2334,12 +2330,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2652,32 +2648,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129096205</v>
+        <v>129100203</v>
       </c>
       <c r="B21" t="n">
-        <v>96823</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2687,13 +2683,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570898</v>
+        <v>570968</v>
       </c>
       <c r="R21" t="n">
-        <v>7057466</v>
+        <v>7057538</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2723,6 +2719,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2737,44 +2738,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129100203</v>
+        <v>129096205</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>96824</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2784,13 +2785,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570968</v>
+        <v>570898</v>
       </c>
       <c r="R22" t="n">
-        <v>7057538</v>
+        <v>7057466</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2820,11 +2821,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2839,12 +2835,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3583,7 +3579,7 @@
         <v>129092361</v>
       </c>
       <c r="B30" t="n">
-        <v>96823</v>
+        <v>96824</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3687,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129100194</v>
+        <v>129096206</v>
       </c>
       <c r="B31" t="n">
-        <v>5197</v>
+        <v>96824</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3698,21 +3694,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>105930</v>
+        <v>2869</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3722,13 +3718,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571156</v>
+        <v>571159</v>
       </c>
       <c r="R31" t="n">
-        <v>7057504</v>
+        <v>7057565</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3772,22 +3768,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129093045</v>
+        <v>129100194</v>
       </c>
       <c r="B32" t="n">
-        <v>100865</v>
+        <v>5197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3795,34 +3791,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1365</v>
+        <v>105930</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571098</v>
+        <v>571156</v>
       </c>
       <c r="R32" t="n">
-        <v>7057570</v>
+        <v>7057504</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3852,19 +3848,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3879,22 +3865,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129096206</v>
+        <v>129093045</v>
       </c>
       <c r="B33" t="n">
-        <v>96823</v>
+        <v>100867</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,37 +3888,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571159</v>
+        <v>571098</v>
       </c>
       <c r="R33" t="n">
-        <v>7057565</v>
+        <v>7057570</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3959,9 +3945,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3976,12 +3972,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4389,7 +4385,7 @@
         <v>129096204</v>
       </c>
       <c r="B38" t="n">
-        <v>96823</v>
+        <v>96824</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4486,7 +4482,7 @@
         <v>129092519</v>
       </c>
       <c r="B39" t="n">
-        <v>100865</v>
+        <v>100867</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129100217</v>
       </c>
       <c r="B3" t="n">
-        <v>96824</v>
+        <v>96825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129096194</v>
       </c>
       <c r="B7" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1511,51 +1511,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129096203</v>
+        <v>129091918</v>
       </c>
       <c r="B10" t="n">
-        <v>92858</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571163</v>
+        <v>571079</v>
       </c>
       <c r="R10" t="n">
-        <v>7057607</v>
+        <v>7057562</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1582,78 +1579,90 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129091918</v>
+        <v>129096203</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>92858</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571079</v>
+        <v>571163</v>
       </c>
       <c r="R11" t="n">
-        <v>7057562</v>
+        <v>7057607</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1680,39 +1689,30 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1819,7 +1819,7 @@
         <v>129100218</v>
       </c>
       <c r="B13" t="n">
-        <v>96824</v>
+        <v>96825</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>129100211</v>
       </c>
       <c r="B14" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129096197</v>
+        <v>129092795</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,37 +2353,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570925</v>
+        <v>571218</v>
       </c>
       <c r="R18" t="n">
-        <v>7057499</v>
+        <v>7057576</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2410,9 +2415,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2427,22 +2442,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129092795</v>
+        <v>129096197</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2450,42 +2465,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571218</v>
+        <v>570925</v>
       </c>
       <c r="R19" t="n">
-        <v>7057576</v>
+        <v>7057499</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2512,19 +2522,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2539,12 +2539,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2648,32 +2648,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129100203</v>
+        <v>129096205</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>96825</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,13 +2683,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570968</v>
+        <v>570898</v>
       </c>
       <c r="R21" t="n">
-        <v>7057538</v>
+        <v>7057466</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2719,11 +2719,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2738,44 +2733,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129096205</v>
+        <v>129100203</v>
       </c>
       <c r="B22" t="n">
-        <v>96824</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,13 +2780,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570898</v>
+        <v>570968</v>
       </c>
       <c r="R22" t="n">
-        <v>7057466</v>
+        <v>7057538</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2821,6 +2816,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2835,12 +2835,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129100212</v>
+        <v>129100202</v>
       </c>
       <c r="B24" t="n">
-        <v>91536</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,21 +2970,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>570991</v>
+        <v>571055</v>
       </c>
       <c r="R24" t="n">
-        <v>7057492</v>
+        <v>7057572</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,6 +3030,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3056,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129100202</v>
+        <v>129100212</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>91536</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3067,21 +3072,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3091,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571055</v>
+        <v>570991</v>
       </c>
       <c r="R25" t="n">
-        <v>7057572</v>
+        <v>7057492</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3127,11 +3132,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3255,45 +3255,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129093842</v>
+        <v>129091441</v>
       </c>
       <c r="B27" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>570896</v>
+        <v>570938</v>
       </c>
       <c r="R27" t="n">
-        <v>7057451</v>
+        <v>7057605</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3325,7 +3330,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3335,7 +3340,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3362,50 +3372,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129091441</v>
+        <v>129093842</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>570938</v>
+        <v>570896</v>
       </c>
       <c r="R28" t="n">
-        <v>7057605</v>
+        <v>7057451</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3437,7 +3442,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3447,12 +3452,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3479,10 +3479,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129100204</v>
+        <v>129092361</v>
       </c>
       <c r="B29" t="n">
-        <v>80174</v>
+        <v>96825</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3490,34 +3490,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>2869</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>570947</v>
+        <v>571258</v>
       </c>
       <c r="R29" t="n">
-        <v>7057532</v>
+        <v>7057527</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3547,9 +3547,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3564,22 +3574,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129092361</v>
+        <v>129100204</v>
       </c>
       <c r="B30" t="n">
-        <v>96824</v>
+        <v>80174</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3587,34 +3597,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2869</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571258</v>
+        <v>570947</v>
       </c>
       <c r="R30" t="n">
-        <v>7057527</v>
+        <v>7057532</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3644,19 +3654,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3671,22 +3671,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129096206</v>
+        <v>129093045</v>
       </c>
       <c r="B31" t="n">
-        <v>96824</v>
+        <v>100868</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3694,37 +3694,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571159</v>
+        <v>571098</v>
       </c>
       <c r="R31" t="n">
-        <v>7057565</v>
+        <v>7057570</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3751,9 +3751,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3768,22 +3778,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129100194</v>
+        <v>129096206</v>
       </c>
       <c r="B32" t="n">
-        <v>5197</v>
+        <v>96825</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3791,21 +3801,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>105930</v>
+        <v>2869</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3815,13 +3825,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571156</v>
+        <v>571159</v>
       </c>
       <c r="R32" t="n">
-        <v>7057504</v>
+        <v>7057565</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3865,22 +3875,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129093045</v>
+        <v>129100194</v>
       </c>
       <c r="B33" t="n">
-        <v>100867</v>
+        <v>5197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3888,34 +3898,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1365</v>
+        <v>105930</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571098</v>
+        <v>571156</v>
       </c>
       <c r="R33" t="n">
-        <v>7057570</v>
+        <v>7057504</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3945,19 +3955,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3972,12 +3972,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4183,32 +4183,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129100213</v>
+        <v>129096204</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>96825</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4218,13 +4218,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>570948</v>
+        <v>570894</v>
       </c>
       <c r="R36" t="n">
-        <v>7057486</v>
+        <v>7057432</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4268,22 +4268,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129100197</v>
+        <v>129100213</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4291,21 +4291,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570944</v>
+        <v>570948</v>
       </c>
       <c r="R37" t="n">
-        <v>7057538</v>
+        <v>7057486</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4351,11 +4351,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4382,32 +4377,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096204</v>
+        <v>129100197</v>
       </c>
       <c r="B38" t="n">
-        <v>96824</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4417,13 +4412,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>570894</v>
+        <v>570944</v>
       </c>
       <c r="R38" t="n">
-        <v>7057432</v>
+        <v>7057538</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4453,6 +4448,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4467,12 +4467,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4482,7 +4482,7 @@
         <v>129092519</v>
       </c>
       <c r="B39" t="n">
-        <v>100867</v>
+        <v>100868</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129093948</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129100217</v>
       </c>
       <c r="B3" t="n">
-        <v>96825</v>
+        <v>96829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129094000</v>
+        <v>129094090</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +890,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570947</v>
+        <v>571144</v>
       </c>
       <c r="R4" t="n">
-        <v>7057312</v>
+        <v>7057314</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129094153</v>
+        <v>129094000</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571029</v>
+        <v>570947</v>
       </c>
       <c r="R5" t="n">
-        <v>7057276</v>
+        <v>7057312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129094090</v>
+        <v>129094153</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,39 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571144</v>
+        <v>571029</v>
       </c>
       <c r="R6" t="n">
-        <v>7057314</v>
+        <v>7057276</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,12 +1193,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1208,7 +1208,7 @@
         <v>129096194</v>
       </c>
       <c r="B7" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>129093962</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129091918</v>
+        <v>129100200</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,34 +1522,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571079</v>
+        <v>571163</v>
       </c>
       <c r="R10" t="n">
-        <v>7057562</v>
+        <v>7057489</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,19 +1579,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1606,63 +1596,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129096203</v>
+        <v>129091918</v>
       </c>
       <c r="B11" t="n">
-        <v>92858</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571163</v>
+        <v>571079</v>
       </c>
       <c r="R11" t="n">
-        <v>7057607</v>
+        <v>7057562</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1689,65 +1676,77 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129100200</v>
+        <v>129096203</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>92861</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ramariset, Ång</t>
@@ -1757,10 +1756,10 @@
         <v>571163</v>
       </c>
       <c r="R12" t="n">
-        <v>7057489</v>
+        <v>7057607</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1798,50 +1797,51 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129100218</v>
+        <v>129100211</v>
       </c>
       <c r="B13" t="n">
-        <v>96825</v>
+        <v>98710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570873</v>
+        <v>570948</v>
       </c>
       <c r="R13" t="n">
-        <v>7057429</v>
+        <v>7057495</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,6 +1887,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1913,32 +1918,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129100211</v>
+        <v>129100218</v>
       </c>
       <c r="B14" t="n">
-        <v>98706</v>
+        <v>96829</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570948</v>
+        <v>570873</v>
       </c>
       <c r="R14" t="n">
-        <v>7057495</v>
+        <v>7057429</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1984,11 +1989,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>4 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,7 +2135,7 @@
         <v>129092344</v>
       </c>
       <c r="B16" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>129093213</v>
       </c>
       <c r="B17" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129092795</v>
+        <v>129096197</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,42 +2353,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571218</v>
+        <v>570925</v>
       </c>
       <c r="R18" t="n">
-        <v>7057576</v>
+        <v>7057499</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2415,19 +2410,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2442,22 +2427,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129096197</v>
+        <v>129092795</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,37 +2450,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570925</v>
+        <v>571218</v>
       </c>
       <c r="R19" t="n">
-        <v>7057499</v>
+        <v>7057576</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2522,9 +2512,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2539,12 +2539,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2554,7 +2554,7 @@
         <v>129100214</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2648,32 +2648,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129096205</v>
+        <v>129100203</v>
       </c>
       <c r="B21" t="n">
-        <v>96825</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,13 +2683,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570898</v>
+        <v>570968</v>
       </c>
       <c r="R21" t="n">
-        <v>7057466</v>
+        <v>7057538</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2719,6 +2719,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2733,44 +2738,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129100203</v>
+        <v>129096205</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>96829</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,13 +2785,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570968</v>
+        <v>570898</v>
       </c>
       <c r="R22" t="n">
-        <v>7057538</v>
+        <v>7057466</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2816,11 +2821,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2835,12 +2835,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129100202</v>
+        <v>129100212</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>91539</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,21 +2970,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571055</v>
+        <v>570991</v>
       </c>
       <c r="R24" t="n">
-        <v>7057572</v>
+        <v>7057492</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,11 +3030,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,10 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129100212</v>
+        <v>129100202</v>
       </c>
       <c r="B25" t="n">
-        <v>91536</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3072,21 +3067,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3091,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>570991</v>
+        <v>571055</v>
       </c>
       <c r="R25" t="n">
-        <v>7057492</v>
+        <v>7057572</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,6 +3127,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3161,7 +3161,7 @@
         <v>129096198</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3255,50 +3255,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129091441</v>
+        <v>129093842</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>91507</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>570938</v>
+        <v>570896</v>
       </c>
       <c r="R27" t="n">
-        <v>7057605</v>
+        <v>7057451</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3330,7 +3325,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3340,12 +3335,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3372,45 +3362,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129093842</v>
+        <v>129091441</v>
       </c>
       <c r="B28" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>570896</v>
+        <v>570938</v>
       </c>
       <c r="R28" t="n">
-        <v>7057451</v>
+        <v>7057605</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3442,7 +3437,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3452,7 +3447,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3482,7 +3482,7 @@
         <v>129092361</v>
       </c>
       <c r="B29" t="n">
-        <v>96825</v>
+        <v>96829</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>129100204</v>
       </c>
       <c r="B30" t="n">
-        <v>80174</v>
+        <v>80176</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>129093045</v>
       </c>
       <c r="B31" t="n">
-        <v>100868</v>
+        <v>100872</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>129096206</v>
       </c>
       <c r="B32" t="n">
-        <v>96825</v>
+        <v>96829</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>129100195</v>
       </c>
       <c r="B35" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>129096204</v>
       </c>
       <c r="B36" t="n">
-        <v>96825</v>
+        <v>96829</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>129100213</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4479,45 +4479,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129092519</v>
+        <v>129091900</v>
       </c>
       <c r="B39" t="n">
-        <v>100868</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571253</v>
+        <v>571175</v>
       </c>
       <c r="R39" t="n">
-        <v>7057540</v>
+        <v>7057492</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4549,7 +4554,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4559,7 +4564,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4586,50 +4596,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129091900</v>
+        <v>129092519</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>100872</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571175</v>
+        <v>571253</v>
       </c>
       <c r="R40" t="n">
-        <v>7057492</v>
+        <v>7057540</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4661,7 +4666,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4671,12 +4676,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -3255,45 +3255,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129093842</v>
+        <v>129091441</v>
       </c>
       <c r="B27" t="n">
-        <v>91507</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>570896</v>
+        <v>570938</v>
       </c>
       <c r="R27" t="n">
-        <v>7057451</v>
+        <v>7057605</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3325,7 +3330,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3335,7 +3340,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3362,50 +3372,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129091441</v>
+        <v>129093842</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>91507</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>570938</v>
+        <v>570896</v>
       </c>
       <c r="R28" t="n">
-        <v>7057605</v>
+        <v>7057451</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3437,7 +3442,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3447,12 +3452,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4479,50 +4479,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129091900</v>
+        <v>129092519</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>100872</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571175</v>
+        <v>571253</v>
       </c>
       <c r="R39" t="n">
-        <v>7057492</v>
+        <v>7057540</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4554,7 +4549,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4564,12 +4559,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4596,45 +4586,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129092519</v>
+        <v>129091900</v>
       </c>
       <c r="B40" t="n">
-        <v>100872</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571253</v>
+        <v>571175</v>
       </c>
       <c r="R40" t="n">
-        <v>7057540</v>
+        <v>7057492</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4666,7 +4661,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4676,7 +4671,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129093948</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129100217</v>
       </c>
       <c r="B3" t="n">
-        <v>96829</v>
+        <v>96831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129094090</v>
+        <v>129094000</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571144</v>
+        <v>570947</v>
       </c>
       <c r="R4" t="n">
-        <v>7057314</v>
+        <v>7057312</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +949,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +959,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129094000</v>
+        <v>129094153</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570947</v>
+        <v>571029</v>
       </c>
       <c r="R5" t="n">
-        <v>7057312</v>
+        <v>7057276</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129094153</v>
+        <v>129094090</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,34 +1104,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571029</v>
+        <v>571144</v>
       </c>
       <c r="R6" t="n">
-        <v>7057276</v>
+        <v>7057314</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,12 +1193,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1208,7 +1208,7 @@
         <v>129096194</v>
       </c>
       <c r="B7" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>129093962</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,35 +1511,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129100200</v>
+        <v>129096203</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>92863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramariset, Ång</t>
@@ -1549,10 +1552,10 @@
         <v>571163</v>
       </c>
       <c r="R10" t="n">
-        <v>7057489</v>
+        <v>7057607</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1590,18 +1593,19 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1611,7 +1615,7 @@
         <v>129091918</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,38 +1719,35 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129096203</v>
+        <v>129100200</v>
       </c>
       <c r="B12" t="n">
-        <v>92861</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ramariset, Ång</t>
@@ -1756,10 +1757,10 @@
         <v>571163</v>
       </c>
       <c r="R12" t="n">
-        <v>7057607</v>
+        <v>7057489</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1797,51 +1798,50 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129100211</v>
+        <v>129100218</v>
       </c>
       <c r="B13" t="n">
-        <v>98710</v>
+        <v>96831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570948</v>
+        <v>570873</v>
       </c>
       <c r="R13" t="n">
-        <v>7057495</v>
+        <v>7057429</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,11 +1887,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>4 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1918,32 +1913,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129100218</v>
+        <v>129100211</v>
       </c>
       <c r="B14" t="n">
-        <v>96829</v>
+        <v>98712</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1953,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570873</v>
+        <v>570948</v>
       </c>
       <c r="R14" t="n">
-        <v>7057429</v>
+        <v>7057495</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,6 +1984,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,7 +2135,7 @@
         <v>129092344</v>
       </c>
       <c r="B16" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>129093213</v>
       </c>
       <c r="B17" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129096197</v>
+        <v>129092795</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,37 +2353,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570925</v>
+        <v>571218</v>
       </c>
       <c r="R18" t="n">
-        <v>7057499</v>
+        <v>7057576</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2410,9 +2415,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2427,22 +2442,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129092795</v>
+        <v>129096197</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2450,42 +2465,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571218</v>
+        <v>570925</v>
       </c>
       <c r="R19" t="n">
-        <v>7057576</v>
+        <v>7057499</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2512,19 +2522,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2539,12 +2539,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2554,7 +2554,7 @@
         <v>129100214</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>129096205</v>
       </c>
       <c r="B22" t="n">
-        <v>96829</v>
+        <v>96831</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2959,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129100212</v>
+        <v>129100202</v>
       </c>
       <c r="B24" t="n">
-        <v>91539</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,21 +2970,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>570991</v>
+        <v>571055</v>
       </c>
       <c r="R24" t="n">
-        <v>7057492</v>
+        <v>7057572</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,6 +3030,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3056,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129100202</v>
+        <v>129100212</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>91541</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3067,21 +3072,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3091,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571055</v>
+        <v>570991</v>
       </c>
       <c r="R25" t="n">
-        <v>7057572</v>
+        <v>7057492</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3127,11 +3132,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3161,7 +3161,7 @@
         <v>129096198</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3255,50 +3255,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129091441</v>
+        <v>129093842</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>91509</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>570938</v>
+        <v>570896</v>
       </c>
       <c r="R27" t="n">
-        <v>7057605</v>
+        <v>7057451</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3330,7 +3325,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3340,12 +3335,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3372,45 +3362,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129093842</v>
+        <v>129091441</v>
       </c>
       <c r="B28" t="n">
-        <v>91507</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>570896</v>
+        <v>570938</v>
       </c>
       <c r="R28" t="n">
-        <v>7057451</v>
+        <v>7057605</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3442,7 +3437,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3452,7 +3447,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3479,10 +3479,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129092361</v>
+        <v>129100204</v>
       </c>
       <c r="B29" t="n">
-        <v>96829</v>
+        <v>80177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3490,34 +3490,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2869</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571258</v>
+        <v>570947</v>
       </c>
       <c r="R29" t="n">
-        <v>7057527</v>
+        <v>7057532</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3547,19 +3547,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3574,22 +3564,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129100204</v>
+        <v>129092361</v>
       </c>
       <c r="B30" t="n">
-        <v>80176</v>
+        <v>96831</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3597,34 +3587,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>2869</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>570947</v>
+        <v>571258</v>
       </c>
       <c r="R30" t="n">
-        <v>7057532</v>
+        <v>7057527</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3654,9 +3644,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3671,22 +3671,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129093045</v>
+        <v>129100194</v>
       </c>
       <c r="B31" t="n">
-        <v>100872</v>
+        <v>5197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3694,34 +3694,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1365</v>
+        <v>105930</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571098</v>
+        <v>571156</v>
       </c>
       <c r="R31" t="n">
-        <v>7057570</v>
+        <v>7057504</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3751,19 +3751,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3778,12 +3768,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3793,7 +3783,7 @@
         <v>129096206</v>
       </c>
       <c r="B32" t="n">
-        <v>96829</v>
+        <v>96831</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3887,10 +3877,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129100194</v>
+        <v>129093045</v>
       </c>
       <c r="B33" t="n">
-        <v>5197</v>
+        <v>100874</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3898,34 +3888,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105930</v>
+        <v>1365</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571156</v>
+        <v>571098</v>
       </c>
       <c r="R33" t="n">
-        <v>7057504</v>
+        <v>7057570</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3955,9 +3945,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3972,12 +3972,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4089,7 +4089,7 @@
         <v>129100195</v>
       </c>
       <c r="B35" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,32 +4183,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129096204</v>
+        <v>129100213</v>
       </c>
       <c r="B36" t="n">
-        <v>96829</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4218,13 +4218,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>570894</v>
+        <v>570948</v>
       </c>
       <c r="R36" t="n">
-        <v>7057432</v>
+        <v>7057486</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4268,22 +4268,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129100213</v>
+        <v>129100197</v>
       </c>
       <c r="B37" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4291,21 +4291,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570948</v>
+        <v>570944</v>
       </c>
       <c r="R37" t="n">
-        <v>7057486</v>
+        <v>7057538</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4351,6 +4351,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4377,32 +4382,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129100197</v>
+        <v>129096204</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>96831</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4412,13 +4417,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>570944</v>
+        <v>570894</v>
       </c>
       <c r="R38" t="n">
-        <v>7057538</v>
+        <v>7057432</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4448,11 +4453,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4467,12 +4467,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4482,7 +4482,7 @@
         <v>129092519</v>
       </c>
       <c r="B39" t="n">
-        <v>100872</v>
+        <v>100874</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129100217</v>
       </c>
       <c r="B3" t="n">
-        <v>96831</v>
+        <v>96835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129096194</v>
       </c>
       <c r="B7" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>129096203</v>
       </c>
       <c r="B10" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129091918</v>
+        <v>129100200</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1623,34 +1623,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571079</v>
+        <v>571163</v>
       </c>
       <c r="R11" t="n">
-        <v>7057562</v>
+        <v>7057489</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,19 +1680,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1707,22 +1697,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129100200</v>
+        <v>129091918</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,34 +1720,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571163</v>
+        <v>571079</v>
       </c>
       <c r="R12" t="n">
-        <v>7057489</v>
+        <v>7057562</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,9 +1777,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1804,12 +1804,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1819,7 +1819,7 @@
         <v>129100218</v>
       </c>
       <c r="B13" t="n">
-        <v>96831</v>
+        <v>96835</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>129100211</v>
       </c>
       <c r="B14" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129092344</v>
+        <v>129093213</v>
       </c>
       <c r="B16" t="n">
-        <v>91565</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,19 +2143,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2163,10 +2167,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571249</v>
+        <v>570967</v>
       </c>
       <c r="R16" t="n">
-        <v>7057525</v>
+        <v>7057481</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,7 +2202,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2208,7 +2212,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2223,22 +2227,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129093213</v>
+        <v>129092344</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>91569</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,23 +2250,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570967</v>
+        <v>571249</v>
       </c>
       <c r="R17" t="n">
-        <v>7057481</v>
+        <v>7057525</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2330,22 +2330,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129092795</v>
+        <v>129096197</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,42 +2353,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571218</v>
+        <v>570925</v>
       </c>
       <c r="R18" t="n">
-        <v>7057576</v>
+        <v>7057499</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2415,19 +2410,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2442,22 +2427,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129096197</v>
+        <v>129092795</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,37 +2450,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570925</v>
+        <v>571218</v>
       </c>
       <c r="R19" t="n">
-        <v>7057499</v>
+        <v>7057576</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2522,9 +2512,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2539,12 +2539,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2648,32 +2648,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129100203</v>
+        <v>129096205</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>96835</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,13 +2683,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570968</v>
+        <v>570898</v>
       </c>
       <c r="R21" t="n">
-        <v>7057538</v>
+        <v>7057466</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2719,11 +2719,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2738,44 +2733,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129096205</v>
+        <v>129100203</v>
       </c>
       <c r="B22" t="n">
-        <v>96831</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,13 +2780,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570898</v>
+        <v>570968</v>
       </c>
       <c r="R22" t="n">
-        <v>7057466</v>
+        <v>7057538</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2821,6 +2816,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2835,12 +2835,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129100202</v>
+        <v>129100212</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>91545</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,21 +2970,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571055</v>
+        <v>570991</v>
       </c>
       <c r="R24" t="n">
-        <v>7057572</v>
+        <v>7057492</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,11 +3030,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,10 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129100212</v>
+        <v>129100202</v>
       </c>
       <c r="B25" t="n">
-        <v>91541</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3072,21 +3067,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3091,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>570991</v>
+        <v>571055</v>
       </c>
       <c r="R25" t="n">
-        <v>7057492</v>
+        <v>7057572</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,6 +3127,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3258,7 +3258,7 @@
         <v>129093842</v>
       </c>
       <c r="B27" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129100204</v>
+        <v>129092361</v>
       </c>
       <c r="B29" t="n">
-        <v>80177</v>
+        <v>96835</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3490,34 +3490,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>2869</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>570947</v>
+        <v>571258</v>
       </c>
       <c r="R29" t="n">
-        <v>7057532</v>
+        <v>7057527</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3547,9 +3547,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3564,22 +3574,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129092361</v>
+        <v>129100204</v>
       </c>
       <c r="B30" t="n">
-        <v>96831</v>
+        <v>80177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3587,34 +3597,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2869</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571258</v>
+        <v>570947</v>
       </c>
       <c r="R30" t="n">
-        <v>7057527</v>
+        <v>7057532</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3644,19 +3654,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3671,22 +3671,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129100194</v>
+        <v>129093045</v>
       </c>
       <c r="B31" t="n">
-        <v>5197</v>
+        <v>100878</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3694,34 +3694,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>105930</v>
+        <v>1365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571156</v>
+        <v>571098</v>
       </c>
       <c r="R31" t="n">
-        <v>7057504</v>
+        <v>7057570</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3751,9 +3751,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3768,12 +3778,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3783,7 +3793,7 @@
         <v>129096206</v>
       </c>
       <c r="B32" t="n">
-        <v>96831</v>
+        <v>96835</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3877,10 +3887,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129093045</v>
+        <v>129100194</v>
       </c>
       <c r="B33" t="n">
-        <v>100874</v>
+        <v>5197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3888,34 +3898,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1365</v>
+        <v>105930</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571098</v>
+        <v>571156</v>
       </c>
       <c r="R33" t="n">
-        <v>7057570</v>
+        <v>7057504</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3945,19 +3955,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3972,12 +3972,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4089,7 +4089,7 @@
         <v>129100195</v>
       </c>
       <c r="B35" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,32 +4183,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129100213</v>
+        <v>129096204</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>96835</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4218,13 +4218,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>570948</v>
+        <v>570894</v>
       </c>
       <c r="R36" t="n">
-        <v>7057486</v>
+        <v>7057432</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4268,22 +4268,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129100197</v>
+        <v>129100213</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4291,21 +4291,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570944</v>
+        <v>570948</v>
       </c>
       <c r="R37" t="n">
-        <v>7057538</v>
+        <v>7057486</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4351,11 +4351,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4382,32 +4377,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096204</v>
+        <v>129100197</v>
       </c>
       <c r="B38" t="n">
-        <v>96831</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4417,13 +4412,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>570894</v>
+        <v>570944</v>
       </c>
       <c r="R38" t="n">
-        <v>7057432</v>
+        <v>7057538</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4453,6 +4448,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4467,12 +4467,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4482,7 +4482,7 @@
         <v>129092519</v>
       </c>
       <c r="B39" t="n">
-        <v>100874</v>
+        <v>100878</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129100217</v>
       </c>
       <c r="B3" t="n">
-        <v>96835</v>
+        <v>96843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129094000</v>
+        <v>129094090</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +890,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570947</v>
+        <v>571144</v>
       </c>
       <c r="R4" t="n">
-        <v>7057312</v>
+        <v>7057314</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,19 +979,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129094153</v>
+        <v>129094000</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571029</v>
+        <v>570947</v>
       </c>
       <c r="R5" t="n">
-        <v>7057276</v>
+        <v>7057312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129094090</v>
+        <v>129094153</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,39 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571144</v>
+        <v>571029</v>
       </c>
       <c r="R6" t="n">
-        <v>7057314</v>
+        <v>7057276</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,12 +1193,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1208,7 +1208,7 @@
         <v>129096194</v>
       </c>
       <c r="B7" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1511,38 +1511,35 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129096203</v>
+        <v>129100200</v>
       </c>
       <c r="B10" t="n">
-        <v>92867</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramariset, Ång</t>
@@ -1552,10 +1549,10 @@
         <v>571163</v>
       </c>
       <c r="R10" t="n">
-        <v>7057607</v>
+        <v>7057489</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,54 +1590,56 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129100200</v>
+        <v>129096203</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>92868</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ramariset, Ång</t>
@@ -1650,10 +1649,10 @@
         <v>571163</v>
       </c>
       <c r="R11" t="n">
-        <v>7057489</v>
+        <v>7057607</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1691,18 +1690,19 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1819,7 +1819,7 @@
         <v>129100218</v>
       </c>
       <c r="B13" t="n">
-        <v>96835</v>
+        <v>96843</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>129100211</v>
       </c>
       <c r="B14" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>129092344</v>
       </c>
       <c r="B17" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>129096205</v>
       </c>
       <c r="B21" t="n">
-        <v>96835</v>
+        <v>96843</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2959,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129100212</v>
+        <v>129100202</v>
       </c>
       <c r="B24" t="n">
-        <v>91545</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,21 +2970,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>570991</v>
+        <v>571055</v>
       </c>
       <c r="R24" t="n">
-        <v>7057492</v>
+        <v>7057572</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,6 +3030,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3056,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129100202</v>
+        <v>129100212</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>91546</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3067,21 +3072,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3091,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571055</v>
+        <v>570991</v>
       </c>
       <c r="R25" t="n">
-        <v>7057572</v>
+        <v>7057492</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3127,11 +3132,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3258,7 +3258,7 @@
         <v>129093842</v>
       </c>
       <c r="B27" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>129092361</v>
       </c>
       <c r="B29" t="n">
-        <v>96835</v>
+        <v>96843</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>129093045</v>
       </c>
       <c r="B31" t="n">
-        <v>100878</v>
+        <v>100886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>129096206</v>
       </c>
       <c r="B32" t="n">
-        <v>96835</v>
+        <v>96843</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>129100195</v>
       </c>
       <c r="B35" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>129096204</v>
       </c>
       <c r="B36" t="n">
-        <v>96835</v>
+        <v>96843</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129100213</v>
+        <v>129100197</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4291,21 +4291,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570948</v>
+        <v>570944</v>
       </c>
       <c r="R37" t="n">
-        <v>7057486</v>
+        <v>7057538</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4351,6 +4351,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4377,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129100197</v>
+        <v>129100213</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4388,21 +4393,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4412,10 +4417,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>570944</v>
+        <v>570948</v>
       </c>
       <c r="R38" t="n">
-        <v>7057538</v>
+        <v>7057486</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4448,11 +4453,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4482,7 +4482,7 @@
         <v>129092519</v>
       </c>
       <c r="B39" t="n">
-        <v>100878</v>
+        <v>100886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129094090</v>
+        <v>129094000</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571144</v>
+        <v>570947</v>
       </c>
       <c r="R4" t="n">
-        <v>7057314</v>
+        <v>7057312</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +949,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +959,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,19 +974,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129094000</v>
+        <v>129094153</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570947</v>
+        <v>571029</v>
       </c>
       <c r="R5" t="n">
-        <v>7057312</v>
+        <v>7057276</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129094153</v>
+        <v>129094090</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,34 +1104,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571029</v>
+        <v>571144</v>
       </c>
       <c r="R6" t="n">
-        <v>7057276</v>
+        <v>7057314</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,12 +1193,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1511,35 +1511,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129100200</v>
+        <v>129096203</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>92868</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramariset, Ång</t>
@@ -1549,10 +1552,10 @@
         <v>571163</v>
       </c>
       <c r="R10" t="n">
-        <v>7057489</v>
+        <v>7057607</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1590,69 +1593,67 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129096203</v>
+        <v>129091918</v>
       </c>
       <c r="B11" t="n">
-        <v>92868</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571163</v>
+        <v>571079</v>
       </c>
       <c r="R11" t="n">
-        <v>7057607</v>
+        <v>7057562</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1679,40 +1680,49 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129091918</v>
+        <v>129100200</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1720,34 +1730,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571079</v>
+        <v>571163</v>
       </c>
       <c r="R12" t="n">
-        <v>7057562</v>
+        <v>7057489</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,19 +1787,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1804,12 +1804,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2648,32 +2648,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129096205</v>
+        <v>129100203</v>
       </c>
       <c r="B21" t="n">
-        <v>96843</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,13 +2683,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570898</v>
+        <v>570968</v>
       </c>
       <c r="R21" t="n">
-        <v>7057466</v>
+        <v>7057538</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2719,6 +2719,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2733,44 +2738,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129100203</v>
+        <v>129096205</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>96843</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,13 +2785,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570968</v>
+        <v>570898</v>
       </c>
       <c r="R22" t="n">
-        <v>7057538</v>
+        <v>7057466</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2816,11 +2821,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2835,12 +2835,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129100202</v>
+        <v>129100212</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>91546</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,21 +2970,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571055</v>
+        <v>570991</v>
       </c>
       <c r="R24" t="n">
-        <v>7057572</v>
+        <v>7057492</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,11 +3030,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,10 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129100212</v>
+        <v>129100202</v>
       </c>
       <c r="B25" t="n">
-        <v>91546</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3072,21 +3067,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3091,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>570991</v>
+        <v>571055</v>
       </c>
       <c r="R25" t="n">
-        <v>7057492</v>
+        <v>7057572</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,6 +3127,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3479,10 +3479,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129092361</v>
+        <v>129100204</v>
       </c>
       <c r="B29" t="n">
-        <v>96843</v>
+        <v>80177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3490,34 +3490,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2869</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571258</v>
+        <v>570947</v>
       </c>
       <c r="R29" t="n">
-        <v>7057527</v>
+        <v>7057532</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3547,19 +3547,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3574,22 +3564,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129100204</v>
+        <v>129092361</v>
       </c>
       <c r="B30" t="n">
-        <v>80177</v>
+        <v>96843</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3597,34 +3587,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>2869</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>570947</v>
+        <v>571258</v>
       </c>
       <c r="R30" t="n">
-        <v>7057532</v>
+        <v>7057527</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3654,9 +3644,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3671,12 +3671,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3790,10 +3790,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129096206</v>
+        <v>129100194</v>
       </c>
       <c r="B32" t="n">
-        <v>96843</v>
+        <v>5197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3801,21 +3801,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2869</v>
+        <v>105930</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3825,13 +3825,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571159</v>
+        <v>571156</v>
       </c>
       <c r="R32" t="n">
-        <v>7057565</v>
+        <v>7057504</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3875,22 +3875,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129100194</v>
+        <v>129096206</v>
       </c>
       <c r="B33" t="n">
-        <v>5197</v>
+        <v>96843</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3898,21 +3898,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105930</v>
+        <v>2869</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3922,13 +3922,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571156</v>
+        <v>571159</v>
       </c>
       <c r="R33" t="n">
-        <v>7057504</v>
+        <v>7057565</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3972,12 +3972,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4183,32 +4183,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129096204</v>
+        <v>129100213</v>
       </c>
       <c r="B36" t="n">
-        <v>96843</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4218,13 +4218,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>570894</v>
+        <v>570948</v>
       </c>
       <c r="R36" t="n">
-        <v>7057432</v>
+        <v>7057486</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4268,12 +4268,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4382,32 +4382,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129100213</v>
+        <v>129096204</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>96843</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4417,13 +4417,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>570948</v>
+        <v>570894</v>
       </c>
       <c r="R38" t="n">
-        <v>7057486</v>
+        <v>7057432</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4467,57 +4467,62 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129092519</v>
+        <v>129091900</v>
       </c>
       <c r="B39" t="n">
-        <v>100886</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571253</v>
+        <v>571175</v>
       </c>
       <c r="R39" t="n">
-        <v>7057540</v>
+        <v>7057492</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4549,7 +4554,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4559,7 +4564,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4586,50 +4596,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129091900</v>
+        <v>129092519</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>100886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571175</v>
+        <v>571253</v>
       </c>
       <c r="R40" t="n">
-        <v>7057492</v>
+        <v>7057540</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4661,7 +4666,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4671,12 +4676,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -3479,10 +3479,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129100204</v>
+        <v>129092361</v>
       </c>
       <c r="B29" t="n">
-        <v>80177</v>
+        <v>96843</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3490,34 +3490,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>2869</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>570947</v>
+        <v>571258</v>
       </c>
       <c r="R29" t="n">
-        <v>7057532</v>
+        <v>7057527</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3547,9 +3547,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3564,22 +3574,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129092361</v>
+        <v>129100204</v>
       </c>
       <c r="B30" t="n">
-        <v>96843</v>
+        <v>80177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3587,34 +3597,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2869</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571258</v>
+        <v>570947</v>
       </c>
       <c r="R30" t="n">
-        <v>7057527</v>
+        <v>7057532</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3644,19 +3654,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3671,22 +3671,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129093045</v>
+        <v>129096206</v>
       </c>
       <c r="B31" t="n">
-        <v>100886</v>
+        <v>96843</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3694,37 +3694,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571098</v>
+        <v>571159</v>
       </c>
       <c r="R31" t="n">
-        <v>7057570</v>
+        <v>7057565</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3751,19 +3751,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3778,22 +3768,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129100194</v>
+        <v>129093045</v>
       </c>
       <c r="B32" t="n">
-        <v>5197</v>
+        <v>100886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3801,34 +3791,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>105930</v>
+        <v>1365</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571156</v>
+        <v>571098</v>
       </c>
       <c r="R32" t="n">
-        <v>7057504</v>
+        <v>7057570</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3858,9 +3848,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3875,22 +3875,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129096206</v>
+        <v>129100194</v>
       </c>
       <c r="B33" t="n">
-        <v>96843</v>
+        <v>5197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3898,21 +3898,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2869</v>
+        <v>105930</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3922,13 +3922,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571159</v>
+        <v>571156</v>
       </c>
       <c r="R33" t="n">
-        <v>7057565</v>
+        <v>7057504</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3972,12 +3972,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129100217</v>
       </c>
       <c r="B3" t="n">
-        <v>96843</v>
+        <v>96846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129096194</v>
       </c>
       <c r="B7" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1511,51 +1511,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129096203</v>
+        <v>129091918</v>
       </c>
       <c r="B10" t="n">
-        <v>92868</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571163</v>
+        <v>571079</v>
       </c>
       <c r="R10" t="n">
-        <v>7057607</v>
+        <v>7057562</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1582,40 +1579,49 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129091918</v>
+        <v>129100200</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1623,34 +1629,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571079</v>
+        <v>571163</v>
       </c>
       <c r="R11" t="n">
-        <v>7057562</v>
+        <v>7057489</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,19 +1686,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1707,47 +1703,50 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129100200</v>
+        <v>129096203</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>92871</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ramariset, Ång</t>
@@ -1757,10 +1756,10 @@
         <v>571163</v>
       </c>
       <c r="R12" t="n">
-        <v>7057489</v>
+        <v>7057607</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1798,18 +1797,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1819,7 +1819,7 @@
         <v>129100218</v>
       </c>
       <c r="B13" t="n">
-        <v>96843</v>
+        <v>96846</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>129100211</v>
       </c>
       <c r="B14" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129093213</v>
+        <v>129092344</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>91573</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,23 +2143,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2167,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570967</v>
+        <v>571249</v>
       </c>
       <c r="R16" t="n">
-        <v>7057481</v>
+        <v>7057525</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,7 +2198,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2212,7 +2208,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2227,22 +2223,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129092344</v>
+        <v>129093213</v>
       </c>
       <c r="B17" t="n">
-        <v>91570</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,19 +2246,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571249</v>
+        <v>570967</v>
       </c>
       <c r="R17" t="n">
-        <v>7057525</v>
+        <v>7057481</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2330,12 +2330,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2648,32 +2648,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129100203</v>
+        <v>129096205</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>96846</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,13 +2683,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570968</v>
+        <v>570898</v>
       </c>
       <c r="R21" t="n">
-        <v>7057538</v>
+        <v>7057466</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2719,11 +2719,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2738,44 +2733,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129096205</v>
+        <v>129100203</v>
       </c>
       <c r="B22" t="n">
-        <v>96843</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,13 +2780,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570898</v>
+        <v>570968</v>
       </c>
       <c r="R22" t="n">
-        <v>7057466</v>
+        <v>7057538</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2821,6 +2816,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2835,12 +2835,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2962,7 +2962,7 @@
         <v>129100212</v>
       </c>
       <c r="B24" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>129093842</v>
       </c>
       <c r="B27" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>129092361</v>
       </c>
       <c r="B29" t="n">
-        <v>96843</v>
+        <v>96846</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129096206</v>
+        <v>129093045</v>
       </c>
       <c r="B31" t="n">
-        <v>96843</v>
+        <v>100889</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3694,37 +3694,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571159</v>
+        <v>571098</v>
       </c>
       <c r="R31" t="n">
-        <v>7057565</v>
+        <v>7057570</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3751,9 +3751,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3768,22 +3778,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129093045</v>
+        <v>129096206</v>
       </c>
       <c r="B32" t="n">
-        <v>100886</v>
+        <v>96846</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3791,37 +3801,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571098</v>
+        <v>571159</v>
       </c>
       <c r="R32" t="n">
-        <v>7057570</v>
+        <v>7057565</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3848,19 +3858,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3875,12 +3875,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4089,7 +4089,7 @@
         <v>129100195</v>
       </c>
       <c r="B35" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,32 +4183,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129100213</v>
+        <v>129096204</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>96846</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4218,13 +4218,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>570948</v>
+        <v>570894</v>
       </c>
       <c r="R36" t="n">
-        <v>7057486</v>
+        <v>7057432</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4268,22 +4268,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129100197</v>
+        <v>129100213</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4291,21 +4291,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570944</v>
+        <v>570948</v>
       </c>
       <c r="R37" t="n">
-        <v>7057538</v>
+        <v>7057486</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4351,11 +4351,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4382,32 +4377,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096204</v>
+        <v>129100197</v>
       </c>
       <c r="B38" t="n">
-        <v>96843</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4417,13 +4412,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>570894</v>
+        <v>570944</v>
       </c>
       <c r="R38" t="n">
-        <v>7057432</v>
+        <v>7057538</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4453,6 +4448,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4467,62 +4467,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129091900</v>
+        <v>129092519</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>100889</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571175</v>
+        <v>571253</v>
       </c>
       <c r="R39" t="n">
-        <v>7057492</v>
+        <v>7057540</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4554,7 +4549,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4564,12 +4559,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4596,45 +4586,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129092519</v>
+        <v>129091900</v>
       </c>
       <c r="B40" t="n">
-        <v>100886</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571253</v>
+        <v>571175</v>
       </c>
       <c r="R40" t="n">
-        <v>7057540</v>
+        <v>7057492</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4666,7 +4661,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4676,7 +4671,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129094000</v>
+        <v>129094090</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +890,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570947</v>
+        <v>571144</v>
       </c>
       <c r="R4" t="n">
-        <v>7057312</v>
+        <v>7057314</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129094090</v>
+        <v>129094000</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,39 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571144</v>
+        <v>570947</v>
       </c>
       <c r="R6" t="n">
-        <v>7057314</v>
+        <v>7057312</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,12 +1193,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1511,48 +1511,51 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129091918</v>
+        <v>129096203</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>92871</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571079</v>
+        <v>571163</v>
       </c>
       <c r="R10" t="n">
-        <v>7057562</v>
+        <v>7057607</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1579,49 +1582,40 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129100200</v>
+        <v>129091918</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,34 +1623,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571163</v>
+        <v>571079</v>
       </c>
       <c r="R11" t="n">
-        <v>7057489</v>
+        <v>7057562</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,9 +1680,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,50 +1707,47 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129096203</v>
+        <v>129100200</v>
       </c>
       <c r="B12" t="n">
-        <v>92871</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ramariset, Ång</t>
@@ -1756,10 +1757,10 @@
         <v>571163</v>
       </c>
       <c r="R12" t="n">
-        <v>7057607</v>
+        <v>7057489</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1797,19 +1798,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129092344</v>
+        <v>129093213</v>
       </c>
       <c r="B16" t="n">
-        <v>91573</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,19 +2143,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2163,10 +2167,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571249</v>
+        <v>570967</v>
       </c>
       <c r="R16" t="n">
-        <v>7057525</v>
+        <v>7057481</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,7 +2202,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2208,7 +2212,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2223,22 +2227,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129093213</v>
+        <v>129092344</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>91573</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,23 +2250,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570967</v>
+        <v>571249</v>
       </c>
       <c r="R17" t="n">
-        <v>7057481</v>
+        <v>7057525</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2330,12 +2330,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2648,32 +2648,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129096205</v>
+        <v>129100203</v>
       </c>
       <c r="B21" t="n">
-        <v>96846</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,13 +2683,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570898</v>
+        <v>570968</v>
       </c>
       <c r="R21" t="n">
-        <v>7057466</v>
+        <v>7057538</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2719,6 +2719,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2733,44 +2738,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129100203</v>
+        <v>129096205</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>96846</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,13 +2785,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570968</v>
+        <v>570898</v>
       </c>
       <c r="R22" t="n">
-        <v>7057538</v>
+        <v>7057466</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2816,11 +2821,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2835,12 +2835,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129100212</v>
+        <v>129100202</v>
       </c>
       <c r="B24" t="n">
-        <v>91549</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,21 +2970,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>570991</v>
+        <v>571055</v>
       </c>
       <c r="R24" t="n">
-        <v>7057492</v>
+        <v>7057572</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,6 +3030,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3056,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129100202</v>
+        <v>129100212</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>91549</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3067,21 +3072,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3091,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571055</v>
+        <v>570991</v>
       </c>
       <c r="R25" t="n">
-        <v>7057572</v>
+        <v>7057492</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3127,11 +3132,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3479,10 +3479,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129092361</v>
+        <v>129100204</v>
       </c>
       <c r="B29" t="n">
-        <v>96846</v>
+        <v>80177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3490,34 +3490,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2869</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571258</v>
+        <v>570947</v>
       </c>
       <c r="R29" t="n">
-        <v>7057527</v>
+        <v>7057532</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3547,19 +3547,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3574,22 +3564,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129100204</v>
+        <v>129092361</v>
       </c>
       <c r="B30" t="n">
-        <v>80177</v>
+        <v>96846</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3597,34 +3587,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>2869</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>570947</v>
+        <v>571258</v>
       </c>
       <c r="R30" t="n">
-        <v>7057532</v>
+        <v>7057527</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3654,9 +3644,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3671,12 +3671,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4280,10 +4280,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129100213</v>
+        <v>129100197</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4291,21 +4291,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570948</v>
+        <v>570944</v>
       </c>
       <c r="R37" t="n">
-        <v>7057486</v>
+        <v>7057538</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4351,6 +4351,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4377,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129100197</v>
+        <v>129100213</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4388,21 +4393,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4412,10 +4417,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>570944</v>
+        <v>570948</v>
       </c>
       <c r="R38" t="n">
-        <v>7057538</v>
+        <v>7057486</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4448,11 +4453,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4479,45 +4479,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129092519</v>
+        <v>129091900</v>
       </c>
       <c r="B39" t="n">
-        <v>100889</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571253</v>
+        <v>571175</v>
       </c>
       <c r="R39" t="n">
-        <v>7057540</v>
+        <v>7057492</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4549,7 +4554,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4559,7 +4564,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4586,50 +4596,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129091900</v>
+        <v>129092519</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>100889</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571175</v>
+        <v>571253</v>
       </c>
       <c r="R40" t="n">
-        <v>7057492</v>
+        <v>7057540</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4661,7 +4666,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4671,12 +4676,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129094090</v>
+        <v>129094000</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571144</v>
+        <v>570947</v>
       </c>
       <c r="R4" t="n">
-        <v>7057314</v>
+        <v>7057312</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +949,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +959,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,12 +974,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129094000</v>
+        <v>129094090</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,34 +1104,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570947</v>
+        <v>571144</v>
       </c>
       <c r="R6" t="n">
-        <v>7057312</v>
+        <v>7057314</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,12 +1193,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1511,51 +1511,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129096203</v>
+        <v>129091918</v>
       </c>
       <c r="B10" t="n">
-        <v>92871</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571163</v>
+        <v>571079</v>
       </c>
       <c r="R10" t="n">
-        <v>7057607</v>
+        <v>7057562</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1582,78 +1579,90 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129091918</v>
+        <v>129096203</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>92871</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571079</v>
+        <v>571163</v>
       </c>
       <c r="R11" t="n">
-        <v>7057562</v>
+        <v>7057607</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1680,39 +1689,30 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129093213</v>
+        <v>129092344</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>91573</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,23 +2143,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2167,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570967</v>
+        <v>571249</v>
       </c>
       <c r="R16" t="n">
-        <v>7057481</v>
+        <v>7057525</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,7 +2198,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2212,7 +2208,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2227,22 +2223,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129092344</v>
+        <v>129093213</v>
       </c>
       <c r="B17" t="n">
-        <v>91573</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,19 +2246,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571249</v>
+        <v>570967</v>
       </c>
       <c r="R17" t="n">
-        <v>7057525</v>
+        <v>7057481</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2330,12 +2330,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2648,32 +2648,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129100203</v>
+        <v>129096205</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>96846</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,13 +2683,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570968</v>
+        <v>570898</v>
       </c>
       <c r="R21" t="n">
-        <v>7057538</v>
+        <v>7057466</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2719,11 +2719,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2738,44 +2733,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129096205</v>
+        <v>129100203</v>
       </c>
       <c r="B22" t="n">
-        <v>96846</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,13 +2780,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570898</v>
+        <v>570968</v>
       </c>
       <c r="R22" t="n">
-        <v>7057466</v>
+        <v>7057538</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2821,6 +2816,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2835,12 +2835,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129100202</v>
+        <v>129100212</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>91549</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,21 +2970,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571055</v>
+        <v>570991</v>
       </c>
       <c r="R24" t="n">
-        <v>7057572</v>
+        <v>7057492</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,11 +3030,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,10 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129100212</v>
+        <v>129100202</v>
       </c>
       <c r="B25" t="n">
-        <v>91549</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3072,21 +3067,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3091,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>570991</v>
+        <v>571055</v>
       </c>
       <c r="R25" t="n">
-        <v>7057492</v>
+        <v>7057572</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,6 +3127,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3479,10 +3479,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129100204</v>
+        <v>129092361</v>
       </c>
       <c r="B29" t="n">
-        <v>80177</v>
+        <v>96846</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3490,34 +3490,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>2869</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>570947</v>
+        <v>571258</v>
       </c>
       <c r="R29" t="n">
-        <v>7057532</v>
+        <v>7057527</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3547,9 +3547,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3564,22 +3574,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129092361</v>
+        <v>129100204</v>
       </c>
       <c r="B30" t="n">
-        <v>96846</v>
+        <v>80177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3587,34 +3597,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2869</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571258</v>
+        <v>570947</v>
       </c>
       <c r="R30" t="n">
-        <v>7057527</v>
+        <v>7057532</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3644,19 +3654,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3671,22 +3671,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129093045</v>
+        <v>129096206</v>
       </c>
       <c r="B31" t="n">
-        <v>100889</v>
+        <v>96846</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3694,37 +3694,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571098</v>
+        <v>571159</v>
       </c>
       <c r="R31" t="n">
-        <v>7057570</v>
+        <v>7057565</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3751,19 +3751,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3778,22 +3768,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129096206</v>
+        <v>129093045</v>
       </c>
       <c r="B32" t="n">
-        <v>96846</v>
+        <v>100889</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3801,37 +3791,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571159</v>
+        <v>571098</v>
       </c>
       <c r="R32" t="n">
-        <v>7057565</v>
+        <v>7057570</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3858,9 +3848,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3875,12 +3875,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4183,32 +4183,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129096204</v>
+        <v>129100213</v>
       </c>
       <c r="B36" t="n">
-        <v>96846</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4218,13 +4218,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>570894</v>
+        <v>570948</v>
       </c>
       <c r="R36" t="n">
-        <v>7057432</v>
+        <v>7057486</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4268,44 +4268,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129100197</v>
+        <v>129096204</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>96846</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4315,13 +4315,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570944</v>
+        <v>570894</v>
       </c>
       <c r="R37" t="n">
-        <v>7057538</v>
+        <v>7057432</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4351,11 +4351,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4370,22 +4365,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129100213</v>
+        <v>129100197</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,21 +4388,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4417,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>570948</v>
+        <v>570944</v>
       </c>
       <c r="R38" t="n">
-        <v>7057486</v>
+        <v>7057538</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4453,6 +4448,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4479,50 +4479,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129091900</v>
+        <v>129092519</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>100889</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571175</v>
+        <v>571253</v>
       </c>
       <c r="R39" t="n">
-        <v>7057492</v>
+        <v>7057540</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4554,7 +4549,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4564,12 +4559,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4596,45 +4586,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129092519</v>
+        <v>129091900</v>
       </c>
       <c r="B40" t="n">
-        <v>100889</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571253</v>
+        <v>571175</v>
       </c>
       <c r="R40" t="n">
-        <v>7057540</v>
+        <v>7057492</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4666,7 +4661,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4676,7 +4671,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129096197</v>
+        <v>129092795</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,37 +2353,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570925</v>
+        <v>571218</v>
       </c>
       <c r="R18" t="n">
-        <v>7057499</v>
+        <v>7057576</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2410,9 +2415,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2427,22 +2442,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129092795</v>
+        <v>129096197</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2450,42 +2465,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571218</v>
+        <v>570925</v>
       </c>
       <c r="R19" t="n">
-        <v>7057576</v>
+        <v>7057499</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2512,19 +2522,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2539,12 +2539,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -4280,32 +4280,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129096204</v>
+        <v>129100197</v>
       </c>
       <c r="B37" t="n">
-        <v>96846</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4315,13 +4315,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570894</v>
+        <v>570944</v>
       </c>
       <c r="R37" t="n">
-        <v>7057432</v>
+        <v>7057538</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4351,6 +4351,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4365,44 +4370,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129100197</v>
+        <v>129096204</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>96846</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4412,13 +4417,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>570944</v>
+        <v>570894</v>
       </c>
       <c r="R38" t="n">
-        <v>7057538</v>
+        <v>7057432</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4448,11 +4453,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4467,12 +4467,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129094000</v>
+        <v>129094090</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +890,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570947</v>
+        <v>571144</v>
       </c>
       <c r="R4" t="n">
-        <v>7057312</v>
+        <v>7057314</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,19 +979,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129094153</v>
+        <v>129094000</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571029</v>
+        <v>570947</v>
       </c>
       <c r="R5" t="n">
-        <v>7057276</v>
+        <v>7057312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129094090</v>
+        <v>129094153</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,39 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571144</v>
+        <v>571029</v>
       </c>
       <c r="R6" t="n">
-        <v>7057314</v>
+        <v>7057276</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,12 +1193,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1618,38 +1618,35 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129096203</v>
+        <v>129100200</v>
       </c>
       <c r="B11" t="n">
-        <v>92871</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ramariset, Ång</t>
@@ -1659,10 +1656,10 @@
         <v>571163</v>
       </c>
       <c r="R11" t="n">
-        <v>7057607</v>
+        <v>7057489</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,54 +1697,56 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129100200</v>
+        <v>129096203</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>92871</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ramariset, Ång</t>
@@ -1757,10 +1756,10 @@
         <v>571163</v>
       </c>
       <c r="R12" t="n">
-        <v>7057489</v>
+        <v>7057607</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1798,18 +1797,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129096206</v>
+        <v>129093045</v>
       </c>
       <c r="B31" t="n">
-        <v>96846</v>
+        <v>100889</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3694,37 +3694,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571159</v>
+        <v>571098</v>
       </c>
       <c r="R31" t="n">
-        <v>7057565</v>
+        <v>7057570</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3751,9 +3751,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3768,22 +3778,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129093045</v>
+        <v>129096206</v>
       </c>
       <c r="B32" t="n">
-        <v>100889</v>
+        <v>96846</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3791,37 +3801,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571098</v>
+        <v>571159</v>
       </c>
       <c r="R32" t="n">
-        <v>7057570</v>
+        <v>7057565</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3848,19 +3858,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3875,12 +3875,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4183,32 +4183,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129100213</v>
+        <v>129096204</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>96846</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4218,13 +4218,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>570948</v>
+        <v>570894</v>
       </c>
       <c r="R36" t="n">
-        <v>7057486</v>
+        <v>7057432</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4268,22 +4268,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129100197</v>
+        <v>129100213</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4291,21 +4291,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570944</v>
+        <v>570948</v>
       </c>
       <c r="R37" t="n">
-        <v>7057538</v>
+        <v>7057486</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4351,11 +4351,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4382,32 +4377,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096204</v>
+        <v>129100197</v>
       </c>
       <c r="B38" t="n">
-        <v>96846</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4417,13 +4412,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>570894</v>
+        <v>570944</v>
       </c>
       <c r="R38" t="n">
-        <v>7057432</v>
+        <v>7057538</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4453,6 +4448,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4467,12 +4467,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129093948</v>
+        <v>129100212</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570884</v>
+        <v>570991</v>
       </c>
       <c r="R2" t="n">
-        <v>7057359</v>
+        <v>7057492</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,44 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129100217</v>
+        <v>129096193</v>
       </c>
       <c r="B3" t="n">
-        <v>96846</v>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571029</v>
+        <v>571216</v>
       </c>
       <c r="R3" t="n">
-        <v>7057300</v>
+        <v>7057561</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,62 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129094090</v>
+        <v>129092519</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>101298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571144</v>
+        <v>571253</v>
       </c>
       <c r="R4" t="n">
-        <v>7057314</v>
+        <v>7057540</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +939,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +949,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129094000</v>
+        <v>129093045</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>101298</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570947</v>
+        <v>571098</v>
       </c>
       <c r="R5" t="n">
-        <v>7057312</v>
+        <v>7057570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1046,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1056,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,44 +1071,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129094153</v>
+        <v>129092361</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>97231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571029</v>
+        <v>571258</v>
       </c>
       <c r="R6" t="n">
-        <v>7057276</v>
+        <v>7057527</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1153,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1163,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129096194</v>
+        <v>129096204</v>
       </c>
       <c r="B7" t="n">
-        <v>97598</v>
+        <v>97231</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570918</v>
+        <v>570894</v>
       </c>
       <c r="R7" t="n">
-        <v>7057413</v>
+        <v>7057432</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1302,48 +1287,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129093962</v>
+        <v>129096205</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>97231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570899</v>
+        <v>570898</v>
       </c>
       <c r="R8" t="n">
-        <v>7057345</v>
+        <v>7057466</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1370,19 +1355,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,44 +1372,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129100196</v>
+        <v>129096206</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>97231</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,13 +1419,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570887</v>
+        <v>571159</v>
       </c>
       <c r="R9" t="n">
-        <v>7057326</v>
+        <v>7057565</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1480,11 +1455,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,57 +1469,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129091918</v>
+        <v>129100217</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>97231</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571079</v>
+        <v>571029</v>
       </c>
       <c r="R10" t="n">
-        <v>7057562</v>
+        <v>7057300</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,19 +1549,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1606,44 +1566,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129100200</v>
+        <v>129100218</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>97231</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571163</v>
+        <v>570873</v>
       </c>
       <c r="R11" t="n">
-        <v>7057489</v>
+        <v>7057429</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,10 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129096203</v>
+        <v>129093842</v>
       </c>
       <c r="B12" t="n">
-        <v>92871</v>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,40 +1686,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571163</v>
+        <v>570896</v>
       </c>
       <c r="R12" t="n">
-        <v>7057607</v>
+        <v>7057451</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1786,40 +1743,49 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129100218</v>
+        <v>129100195</v>
       </c>
       <c r="B13" t="n">
-        <v>96846</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1827,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570873</v>
+        <v>571180</v>
       </c>
       <c r="R13" t="n">
-        <v>7057429</v>
+        <v>7057506</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,48 +1879,51 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129100211</v>
+        <v>129096203</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>93233</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570948</v>
+        <v>571163</v>
       </c>
       <c r="R14" t="n">
-        <v>7057495</v>
+        <v>7057607</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1986,79 +1955,70 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>4 ex</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129091516</v>
+        <v>129091918</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570993</v>
+        <v>571079</v>
       </c>
       <c r="R15" t="n">
-        <v>7057554</v>
+        <v>7057562</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2090,7 +2050,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2100,12 +2060,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska &amp; äldre ringhack på tall</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2120,42 +2075,46 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129092344</v>
+        <v>129093948</v>
       </c>
       <c r="B16" t="n">
-        <v>91573</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2163,10 +2122,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571249</v>
+        <v>570884</v>
       </c>
       <c r="R16" t="n">
-        <v>7057525</v>
+        <v>7057359</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,7 +2157,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2208,7 +2167,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2223,44 +2182,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129093213</v>
+        <v>129093962</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2229,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570967</v>
+        <v>570899</v>
       </c>
       <c r="R17" t="n">
-        <v>7057481</v>
+        <v>7057345</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,7 +2264,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2315,7 +2274,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2342,50 +2301,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129092795</v>
+        <v>129094000</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571218</v>
+        <v>570947</v>
       </c>
       <c r="R18" t="n">
-        <v>7057576</v>
+        <v>7057312</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2417,7 +2371,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2427,7 +2381,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2442,26 +2396,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129096197</v>
+        <v>129094153</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2485,17 +2439,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570925</v>
+        <v>571029</v>
       </c>
       <c r="R19" t="n">
-        <v>7057499</v>
+        <v>7057276</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2522,9 +2476,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2539,26 +2503,26 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129100214</v>
+        <v>129096196</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2586,13 +2550,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570971</v>
+        <v>570897</v>
       </c>
       <c r="R20" t="n">
-        <v>7057531</v>
+        <v>7057417</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2636,44 +2600,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129096205</v>
+        <v>129096197</v>
       </c>
       <c r="B21" t="n">
-        <v>96846</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2647,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570898</v>
+        <v>570925</v>
       </c>
       <c r="R21" t="n">
-        <v>7057466</v>
+        <v>7057499</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2745,32 +2709,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129100203</v>
+        <v>129096198</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,13 +2744,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570968</v>
+        <v>571069</v>
       </c>
       <c r="R22" t="n">
-        <v>7057538</v>
+        <v>7057581</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2816,11 +2780,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2835,62 +2794,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129091908</v>
+        <v>129100213</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571081</v>
+        <v>570948</v>
       </c>
       <c r="R23" t="n">
-        <v>7057568</v>
+        <v>7057486</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2920,19 +2874,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2947,44 +2891,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129100212</v>
+        <v>129100214</v>
       </c>
       <c r="B24" t="n">
-        <v>91549</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,10 +2938,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>570991</v>
+        <v>570971</v>
       </c>
       <c r="R24" t="n">
-        <v>7057492</v>
+        <v>7057531</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3056,10 +3000,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129100202</v>
+        <v>129093213</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3067,34 +3011,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571055</v>
+        <v>570967</v>
       </c>
       <c r="R25" t="n">
-        <v>7057572</v>
+        <v>7057481</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3124,14 +3068,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3146,44 +3095,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129096198</v>
+        <v>129100204</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>80460</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3193,13 +3142,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571069</v>
+        <v>570947</v>
       </c>
       <c r="R26" t="n">
-        <v>7057581</v>
+        <v>7057532</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3243,22 +3192,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129093842</v>
+        <v>129091908</v>
       </c>
       <c r="B27" t="n">
-        <v>91517</v>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3266,34 +3215,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>570896</v>
+        <v>571081</v>
       </c>
       <c r="R27" t="n">
-        <v>7057451</v>
+        <v>7057568</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3325,7 +3279,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3335,7 +3289,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3362,27 +3316,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129091441</v>
+        <v>129092795</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3402,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>570938</v>
+        <v>571218</v>
       </c>
       <c r="R28" t="n">
-        <v>7057605</v>
+        <v>7057576</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3437,7 +3391,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3447,12 +3401,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3467,22 +3416,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129092361</v>
+        <v>129094090</v>
       </c>
       <c r="B29" t="n">
-        <v>96846</v>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3490,34 +3439,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571258</v>
+        <v>571144</v>
       </c>
       <c r="R29" t="n">
-        <v>7057527</v>
+        <v>7057314</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3549,7 +3503,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3559,7 +3513,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3586,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129100204</v>
+        <v>129100201</v>
       </c>
       <c r="B30" t="n">
-        <v>80177</v>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3597,21 +3551,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3621,10 +3575,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>570947</v>
+        <v>571263</v>
       </c>
       <c r="R30" t="n">
-        <v>7057532</v>
+        <v>7057592</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3657,6 +3611,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3683,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129093045</v>
+        <v>129100202</v>
       </c>
       <c r="B31" t="n">
-        <v>100889</v>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3694,34 +3653,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1365</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571098</v>
+        <v>571055</v>
       </c>
       <c r="R31" t="n">
-        <v>7057570</v>
+        <v>7057572</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3751,19 +3710,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:46</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3778,22 +3732,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129096206</v>
+        <v>129100203</v>
       </c>
       <c r="B32" t="n">
-        <v>96846</v>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3801,21 +3755,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3825,13 +3779,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571159</v>
+        <v>570968</v>
       </c>
       <c r="R32" t="n">
-        <v>7057565</v>
+        <v>7057538</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3861,6 +3815,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3875,39 +3834,39 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129100194</v>
+        <v>129091441</v>
       </c>
       <c r="B33" t="n">
-        <v>5197</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3916,16 +3875,21 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571156</v>
+        <v>570938</v>
       </c>
       <c r="R33" t="n">
-        <v>7057504</v>
+        <v>7057605</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3955,9 +3919,24 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3972,22 +3951,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129100201</v>
+        <v>129091516</v>
       </c>
       <c r="B34" t="n">
-        <v>57724</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3995,16 +3974,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4013,16 +3992,21 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>571263</v>
+        <v>570993</v>
       </c>
       <c r="R34" t="n">
-        <v>7057592</v>
+        <v>7057554</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4052,14 +4036,24 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Färska &amp; äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4074,57 +4068,62 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129100195</v>
+        <v>129091900</v>
       </c>
       <c r="B35" t="n">
-        <v>91517</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Lerbäcken, Lerbäcken, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>571180</v>
+        <v>571175</v>
       </c>
       <c r="R35" t="n">
-        <v>7057506</v>
+        <v>7057492</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4154,9 +4153,24 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4171,44 +4185,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129096204</v>
+        <v>129100196</v>
       </c>
       <c r="B36" t="n">
-        <v>96846</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4218,13 +4232,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>570894</v>
+        <v>570887</v>
       </c>
       <c r="R36" t="n">
-        <v>7057432</v>
+        <v>7057326</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4254,6 +4268,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4268,22 +4287,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129100213</v>
+        <v>129100197</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4291,21 +4310,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4315,10 +4334,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570948</v>
+        <v>570944</v>
       </c>
       <c r="R37" t="n">
-        <v>7057486</v>
+        <v>7057538</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4351,6 +4370,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4377,10 +4401,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129100197</v>
+        <v>129096192</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>58114</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4388,21 +4412,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4412,13 +4436,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>570944</v>
+        <v>571123</v>
       </c>
       <c r="R38" t="n">
-        <v>7057538</v>
+        <v>7057613</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4448,11 +4472,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4467,57 +4486,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129092519</v>
+        <v>129100200</v>
       </c>
       <c r="B39" t="n">
-        <v>100889</v>
+        <v>58114</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1365</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571253</v>
+        <v>571163</v>
       </c>
       <c r="R39" t="n">
-        <v>7057540</v>
+        <v>7057489</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4547,19 +4566,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4574,39 +4583,39 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129091900</v>
+        <v>129100194</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>5199</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4615,21 +4624,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571175</v>
+        <v>571156</v>
       </c>
       <c r="R40" t="n">
-        <v>7057492</v>
+        <v>7057504</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4659,24 +4663,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4691,15 +4680,214 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129100211</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ramariset, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>570948</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7057495</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>4 ex</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129096194</v>
+      </c>
+      <c r="B42" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ramariset, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>570918</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7057413</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49356-2025 artfynd.xlsx
+++ b/artfynd/A 49356-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100212</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096193</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129092519</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093045</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129092361</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096204</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096205</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096206</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100217</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100218</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093842</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1876,6 +1936,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100195</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1977,6 +2042,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096203</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2084,6 +2154,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129091918</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2191,6 +2266,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093948</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2298,6 +2378,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093962</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2405,6 +2490,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129094000</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2512,6 +2602,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129094153</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2609,6 +2704,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096196</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2706,6 +2806,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096197</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2803,6 +2908,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096198</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2900,6 +3010,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100213</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2997,6 +3112,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100214</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3104,6 +3224,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093213</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3201,6 +3326,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100204</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3313,6 +3443,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129091908</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3425,6 +3560,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129092795</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3537,6 +3677,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129094090</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3639,6 +3784,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100201</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3741,6 +3891,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100202</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3843,6 +3998,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100203</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3960,6 +4120,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129091441</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4077,6 +4242,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129091516</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4194,6 +4364,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129091900</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4296,6 +4471,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100196</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4398,6 +4578,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100197</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4495,6 +4680,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096192</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4592,6 +4782,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100200</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4689,6 +4884,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100194</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4791,6 +4991,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100211</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4888,8 +5093,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096194</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>